--- a/results/682_z29/5_quantification/682_z29_quantification.xlsx
+++ b/results/682_z29/5_quantification/682_z29_quantification.xlsx
@@ -10,8 +10,9 @@
     <sheet name="per_image" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="width" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="per_lacuna" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="biological_limits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="per_lacuna" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,11 +447,6 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>n_bridges</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,9 +468,6 @@
       <c r="E2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
-        <v>17</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.5455</v>
+        <v>5.3636</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6348</v>
+        <v>1.804</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -735,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>250.2727</v>
+        <v>250.4545</v>
       </c>
       <c r="D13" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E13" t="n">
-        <v>97.6044</v>
+        <v>91.0136</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -764,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>697.4545000000001</v>
+        <v>647.0909</v>
       </c>
       <c r="D14" t="n">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E14" t="n">
-        <v>302.2814</v>
+        <v>247.374</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -793,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>848.5146</v>
+        <v>1557.3019</v>
       </c>
       <c r="D15" t="n">
-        <v>799.7838</v>
+        <v>1262.0042</v>
       </c>
       <c r="E15" t="n">
-        <v>602.7154</v>
+        <v>1443.6751</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -822,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.1818</v>
+        <v>65.9091</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="E16" t="n">
-        <v>22.1667</v>
+        <v>67.58620000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -851,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38.2007</v>
+        <v>25.2613</v>
       </c>
       <c r="D17" t="n">
-        <v>36.5334</v>
+        <v>23.9931</v>
       </c>
       <c r="E17" t="n">
-        <v>13.1105</v>
+        <v>5.9707</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1025,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03152782</v>
+        <v>0.0313798</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03106522</v>
+        <v>0.03133098</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0098891</v>
+        <v>0.00760002</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1054,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03455861</v>
+        <v>0.03234375</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03359533</v>
+        <v>0.03274522</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01017876</v>
+        <v>0.00701619</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1083,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.8431</v>
+        <v>2.7581</v>
       </c>
       <c r="D25" t="n">
         <v>2.7484</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7371</v>
+        <v>0.9127</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1112,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>177.2727</v>
+        <v>186.9091</v>
       </c>
       <c r="D26" t="n">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E26" t="n">
-        <v>70.7758</v>
+        <v>84.6953</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1141,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>349.3636</v>
+        <v>401.6364</v>
       </c>
       <c r="D27" t="n">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="E27" t="n">
-        <v>159.2396</v>
+        <v>227.1824</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1170,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>277.0839</v>
+        <v>277.945</v>
       </c>
       <c r="D28" t="n">
-        <v>272.3087</v>
+        <v>289.5513</v>
       </c>
       <c r="E28" t="n">
-        <v>106.8759</v>
+        <v>98.9509</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1199,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>775.4374</v>
+        <v>723.2128</v>
       </c>
       <c r="D29" t="n">
-        <v>767.2569</v>
+        <v>790.6417</v>
       </c>
       <c r="E29" t="n">
-        <v>337.6027</v>
+        <v>273.2569</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1257,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.454499999999999</v>
+        <v>9.2727</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>3.7514</v>
+        <v>3.6631</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1286,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.4545</v>
+        <v>10.2727</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>4.5247</v>
+        <v>3.7707</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1315,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.0813</v>
+        <v>5.9497</v>
       </c>
       <c r="D33" t="n">
-        <v>5.0395</v>
+        <v>6.2323</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4771</v>
+        <v>0.6796</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1400,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38368</v>
+        <v>29332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03748464</v>
+        <v>0.02865668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1440,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>485</v>
+        <v>537</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00047383</v>
+        <v>0.00052464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1520,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>707</v>
+        <v>289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>54.2687</v>
+        <v>101.4948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04198674</v>
+        <v>0.03240016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1600,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03688309</v>
+        <v>0.02970713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1673,7 +1666,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.7908</v>
+        <v>6.7771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1693,7 +1686,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1713,7 +1706,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1733,7 +1726,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1753,7 +1746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34940</v>
+        <v>28159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1772,1484 +1765,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lacuna_id</t>
+          <t>block</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area_px2</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>major_axis_length_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>minor_axis_length_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>aspect_ratio</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eccentricity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>solidity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>orientation_rad</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>centroid_row_px</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>centroid_col_px</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>on_border</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roots_count</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ring_length_r30_px</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ring_length_r60_px</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>owned_length_px</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>edge_count</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>mean_edge_length_px</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>perimeter_px</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ring_area_r30_px2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ring_area_r60_px2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r30</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r60</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ring_density_r30</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ring_density_r60</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>roots_per_100px_perimeter</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r30_px</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r60_px</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r30_px</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r60_px</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r10</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r20</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r30</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>ring_width_mean_r30_px</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>report only, nothing is pruned or filtered by this block</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>along the network from the owning lacuna's surface to a thread end</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>range_um</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[25.0, 50.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>range_px_applied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[192, 385]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>range_um_applied</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[24.96, 50.05]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>n_threads</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20.677</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4385</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>44.4749</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>max_um</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50.0471</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fraction_in_range</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3929</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fraction_below_range</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6071</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fraction_above_range</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>threads leaving the lacuna surface, interior lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>n_lacunae</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2 x the distance transform of the mask at each sampled skeleton pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>is_an_upper_bound</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>2083</v>
-      </c>
-      <c r="C2" t="n">
-        <v>86.508</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.896</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.479</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.8266</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.5435</v>
-      </c>
-      <c r="I2" t="n">
-        <v>13.4983</v>
-      </c>
-      <c r="J2" t="n">
-        <v>99.4023</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="n">
-        <v>187</v>
-      </c>
-      <c r="N2" t="n">
-        <v>411</v>
-      </c>
-      <c r="O2" t="n">
-        <v>102.669</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>34.223</v>
-      </c>
-      <c r="R2" t="n">
-        <v>262.0955</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5607</v>
-      </c>
-      <c r="T2" t="n">
-        <v>13819</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.5809</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.5584</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.03335117</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.02974166</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.1446</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>92</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>209.9239</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>456.5757</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2213</v>
-      </c>
-      <c r="C3" t="n">
-        <v>89.1614</v>
-      </c>
-      <c r="D3" t="n">
-        <v>32.1486</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.7734</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9327</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.8778</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-1.1291</v>
-      </c>
-      <c r="I3" t="n">
-        <v>134.9137</v>
-      </c>
-      <c r="J3" t="n">
-        <v>921.2924</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>375</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1038.8032</v>
-      </c>
-      <c r="P3" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>29.6801</v>
-      </c>
-      <c r="R3" t="n">
-        <v>229.5219</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9151</v>
-      </c>
-      <c r="T3" t="n">
-        <v>23871</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.04097913</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.04608102</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.4855</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>223</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>425</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>407.3209</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1247.8864</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>5.6666</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>446</v>
-      </c>
-      <c r="C4" t="n">
-        <v>49.6136</v>
-      </c>
-      <c r="D4" t="n">
-        <v>12.2658</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4.0449</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.7866</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-1.4445</v>
-      </c>
-      <c r="I4" t="n">
-        <v>249.9865</v>
-      </c>
-      <c r="J4" t="n">
-        <v>449.3587</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>309</v>
-      </c>
-      <c r="N4" t="n">
-        <v>954</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1414.5433</v>
-      </c>
-      <c r="P4" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>23.1892</v>
-      </c>
-      <c r="R4" t="n">
-        <v>120.8112</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6134</v>
-      </c>
-      <c r="T4" t="n">
-        <v>17911</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.05037496</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.05326336</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.311</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>235</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>440</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>343.5219</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1052.524</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.0395</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3140</v>
-      </c>
-      <c r="C5" t="n">
-        <v>120.6169</v>
-      </c>
-      <c r="D5" t="n">
-        <v>34.4194</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.5043</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9584</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.8885</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.5609</v>
-      </c>
-      <c r="I5" t="n">
-        <v>431.0478</v>
-      </c>
-      <c r="J5" t="n">
-        <v>220.0927</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>352</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1197</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2207.055</v>
-      </c>
-      <c r="P5" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>31.0853</v>
-      </c>
-      <c r="R5" t="n">
-        <v>309.2792</v>
-      </c>
-      <c r="S5" t="n">
-        <v>11331</v>
-      </c>
-      <c r="T5" t="n">
-        <v>28206</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.03106522</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.04243778</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.5867</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>278</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>677</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>390.3209</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1326.4478</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5.3045</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2837</v>
-      </c>
-      <c r="C6" t="n">
-        <v>88.9183</v>
-      </c>
-      <c r="D6" t="n">
-        <v>41.496</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.1428</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.8844</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9229000000000001</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1.5453</v>
-      </c>
-      <c r="I6" t="n">
-        <v>532.0427</v>
-      </c>
-      <c r="J6" t="n">
-        <v>493.0553</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>240</v>
-      </c>
-      <c r="N6" t="n">
-        <v>702</v>
-      </c>
-      <c r="O6" t="n">
-        <v>799.7838</v>
-      </c>
-      <c r="P6" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>36.3538</v>
-      </c>
-      <c r="R6" t="n">
-        <v>235.2376</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9387</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21888</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.02556727</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.03207237</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.1255</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>133</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>278</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>260.3381</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>767.2569</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.8698</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1634</v>
-      </c>
-      <c r="C7" t="n">
-        <v>75.9278</v>
-      </c>
-      <c r="D7" t="n">
-        <v>30.0551</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.5263</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9183</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.8211000000000001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.4797</v>
-      </c>
-      <c r="I7" t="n">
-        <v>555.4829</v>
-      </c>
-      <c r="J7" t="n">
-        <v>357.1867</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>352</v>
-      </c>
-      <c r="N7" t="n">
-        <v>768</v>
-      </c>
-      <c r="O7" t="n">
-        <v>840.2691</v>
-      </c>
-      <c r="P7" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>36.5334</v>
-      </c>
-      <c r="R7" t="n">
-        <v>214.1665</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8637</v>
-      </c>
-      <c r="T7" t="n">
-        <v>20090</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.04075489</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.03822797</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.8016</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>283</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>523</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>399.463</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>865.7666</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.202</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3781</v>
-      </c>
-      <c r="C8" t="n">
-        <v>121.5015</v>
-      </c>
-      <c r="D8" t="n">
-        <v>43.6088</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.7862</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9334</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.8771</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.4272</v>
-      </c>
-      <c r="I8" t="n">
-        <v>590.4819</v>
-      </c>
-      <c r="J8" t="n">
-        <v>55.0987</v>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>9</v>
-      </c>
-      <c r="M8" t="n">
-        <v>319</v>
-      </c>
-      <c r="N8" t="n">
-        <v>716</v>
-      </c>
-      <c r="O8" t="n">
-        <v>857.1686</v>
-      </c>
-      <c r="P8" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>23.1667</v>
-      </c>
-      <c r="R8" t="n">
-        <v>322.8356</v>
-      </c>
-      <c r="S8" t="n">
-        <v>9940</v>
-      </c>
-      <c r="T8" t="n">
-        <v>22198</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.8401999999999999</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.7724</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03209256</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.03225516</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.7878</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>289</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>516</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>349.0366</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>792.3696</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>5.0452</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1399</v>
-      </c>
-      <c r="C9" t="n">
-        <v>81.52</v>
-      </c>
-      <c r="D9" t="n">
-        <v>23.1918</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9587</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8541</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.5542</v>
-      </c>
-      <c r="I9" t="n">
-        <v>716.1351</v>
-      </c>
-      <c r="J9" t="n">
-        <v>181.5704</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>247</v>
-      </c>
-      <c r="N9" t="n">
-        <v>662</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1252.46</v>
-      </c>
-      <c r="P9" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>39.1394</v>
-      </c>
-      <c r="R9" t="n">
-        <v>229.4802</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8595</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22042</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.02873764</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.03003357</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.1788</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>174</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>288</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>272.3087</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>727.6711</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.3423</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>513</v>
-      </c>
-      <c r="C10" t="n">
-        <v>41.8409</v>
-      </c>
-      <c r="D10" t="n">
-        <v>17.3844</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.4068</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9096</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.8607</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.3405</v>
-      </c>
-      <c r="I10" t="n">
-        <v>830.5653</v>
-      </c>
-      <c r="J10" t="n">
-        <v>75.58669999999999</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>143</v>
-      </c>
-      <c r="N10" t="n">
-        <v>391</v>
-      </c>
-      <c r="O10" t="n">
-        <v>410.6346</v>
-      </c>
-      <c r="P10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>37.3304</v>
-      </c>
-      <c r="R10" t="n">
-        <v>109.4975</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4245</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11066</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.9865</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.03368669</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.03533345</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>4.5663</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>124</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>286</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>160.6102</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>434.8478</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.6182</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1130</v>
-      </c>
-      <c r="C11" t="n">
-        <v>64.3164</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.6688</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.7173</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9298</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.8835</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.4062</v>
-      </c>
-      <c r="I11" t="n">
-        <v>842.292</v>
-      </c>
-      <c r="J11" t="n">
-        <v>125.2372</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" t="n">
-        <v>139</v>
-      </c>
-      <c r="N11" t="n">
-        <v>377</v>
-      </c>
-      <c r="O11" t="n">
-        <v>405.4335</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>40.5434</v>
-      </c>
-      <c r="R11" t="n">
-        <v>161.8173</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5491</v>
-      </c>
-      <c r="T11" t="n">
-        <v>13376</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.02531415</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.02818481</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.4719</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>123</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>251</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>159.9533</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>416.463</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>6.0582</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1244</v>
-      </c>
-      <c r="C12" t="n">
-        <v>49.7173</v>
-      </c>
-      <c r="D12" t="n">
-        <v>33.3792</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.4895</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.7411</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.9325</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-1.542</v>
-      </c>
-      <c r="I12" t="n">
-        <v>904.5997</v>
-      </c>
-      <c r="J12" t="n">
-        <v>760.8071</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>97</v>
-      </c>
-      <c r="N12" t="n">
-        <v>352</v>
-      </c>
-      <c r="O12" t="n">
-        <v>213.7939</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>71.2646</v>
-      </c>
-      <c r="R12" t="n">
-        <v>147.196</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6914</v>
-      </c>
-      <c r="T12" t="n">
-        <v>19480</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.01402951</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.01806982</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.0381</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>72</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>138</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>110.8823</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>402.9605</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>4.8201</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2966</v>
-      </c>
-      <c r="C13" t="n">
-        <v>92.1224</v>
-      </c>
-      <c r="D13" t="n">
-        <v>41.6334</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.2127</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.8921</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-1.4899</v>
-      </c>
-      <c r="I13" t="n">
-        <v>920.4009</v>
-      </c>
-      <c r="J13" t="n">
-        <v>307.385</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" t="n">
-        <v>313</v>
-      </c>
-      <c r="N13" t="n">
-        <v>795</v>
-      </c>
-      <c r="O13" t="n">
-        <v>490.0904</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>49.009</v>
-      </c>
-      <c r="R13" t="n">
-        <v>254.6934</v>
-      </c>
-      <c r="S13" t="n">
-        <v>9728</v>
-      </c>
-      <c r="T13" t="n">
-        <v>23664</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.03217516</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.03359533</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.7484</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>193</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>373</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>341.5219</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>875.8255</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.8817</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1624</v>
-      </c>
-      <c r="C14" t="n">
-        <v>72.5441</v>
-      </c>
-      <c r="D14" t="n">
-        <v>29.7651</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.4372</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9119</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.8476</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.945</v>
-      </c>
-      <c r="I14" t="n">
-        <v>978.4969</v>
-      </c>
-      <c r="J14" t="n">
-        <v>437.6151</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" t="n">
-        <v>186</v>
-      </c>
-      <c r="N14" t="n">
-        <v>374</v>
-      </c>
-      <c r="O14" t="n">
-        <v>260.7939</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>26.0794</v>
-      </c>
-      <c r="R14" t="n">
-        <v>202.6934</v>
-      </c>
-      <c r="S14" t="n">
-        <v>7711</v>
-      </c>
-      <c r="T14" t="n">
-        <v>16371</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.9376</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.8055</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.02412139</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.02284528</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.9601</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>112</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>164</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>201.6812</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>412.1615</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>5.0914</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>it includes the optical blur, which widens a thread beyond its true size, and no point spread function is subtracted: the numerical aperture, the emission wavelength and the pinhole are unknown. It is an apparent width in the image, not a canalicular diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -3263,6 +2179,1497 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AG14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lacuna_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>area_px2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>major_axis_length_px</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minor_axis_length_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>orientation_rad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>centroid_row_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>centroid_col_px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>on_border</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mean_edge_length_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ring_width_mean_r30_px</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2083</v>
+      </c>
+      <c r="C2" t="n">
+        <v>86.508</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.896</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8266</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.5435</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13.4983</v>
+      </c>
+      <c r="J2" t="n">
+        <v>99.4023</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N2" t="n">
+        <v>230</v>
+      </c>
+      <c r="O2" t="n">
+        <v>20.4853</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>20.4853</v>
+      </c>
+      <c r="R2" t="n">
+        <v>262.0955</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5607</v>
+      </c>
+      <c r="T2" t="n">
+        <v>13819</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.02282861</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.01664375</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>145.397</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>253.6518</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2213</v>
+      </c>
+      <c r="C3" t="n">
+        <v>89.1614</v>
+      </c>
+      <c r="D3" t="n">
+        <v>32.1486</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.7734</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9327</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8778</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1.1291</v>
+      </c>
+      <c r="I3" t="n">
+        <v>134.9137</v>
+      </c>
+      <c r="J3" t="n">
+        <v>921.2924</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>310</v>
+      </c>
+      <c r="N3" t="n">
+        <v>696</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2661.2237</v>
+      </c>
+      <c r="P3" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>24.1929</v>
+      </c>
+      <c r="R3" t="n">
+        <v>229.5219</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9151</v>
+      </c>
+      <c r="T3" t="n">
+        <v>23871</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.03387608</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.02915672</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.4855</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>259</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>574</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>340.1076</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>791.0681</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.5551</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>446</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49.6136</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12.2658</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.0449</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7866</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.4445</v>
+      </c>
+      <c r="I4" t="n">
+        <v>249.9865</v>
+      </c>
+      <c r="J4" t="n">
+        <v>449.3587</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>263</v>
+      </c>
+      <c r="N4" t="n">
+        <v>566</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2166.4154</v>
+      </c>
+      <c r="P4" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20.6325</v>
+      </c>
+      <c r="R4" t="n">
+        <v>120.8112</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6134</v>
+      </c>
+      <c r="T4" t="n">
+        <v>17911</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.04287577</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.03160069</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.311</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>257</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>557</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>298.3797</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>640.4874</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6.3915</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3140</v>
+      </c>
+      <c r="C5" t="n">
+        <v>120.6169</v>
+      </c>
+      <c r="D5" t="n">
+        <v>34.4194</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.5043</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9584</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5609</v>
+      </c>
+      <c r="I5" t="n">
+        <v>431.0478</v>
+      </c>
+      <c r="J5" t="n">
+        <v>220.0927</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>364</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1180</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5067.8035</v>
+      </c>
+      <c r="P5" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>21.4737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>309.2792</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11331</v>
+      </c>
+      <c r="T5" t="n">
+        <v>28206</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.03212426</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.04183507</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.2633</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>290</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>860</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>401.8356</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1313.5483</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6.3155</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2837</v>
+      </c>
+      <c r="C6" t="n">
+        <v>88.9183</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41.496</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.1428</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8844</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.5453</v>
+      </c>
+      <c r="I6" t="n">
+        <v>532.0427</v>
+      </c>
+      <c r="J6" t="n">
+        <v>493.0553</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>261</v>
+      </c>
+      <c r="N6" t="n">
+        <v>753</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1884.2905</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>28.5499</v>
+      </c>
+      <c r="R6" t="n">
+        <v>235.2376</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9387</v>
+      </c>
+      <c r="T6" t="n">
+        <v>21888</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.02780441</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.03440241</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.7004</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>334</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>279.6102</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>824.1858999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.5492</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1634</v>
+      </c>
+      <c r="C7" t="n">
+        <v>75.9278</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30.0551</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.5263</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8211000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1.4797</v>
+      </c>
+      <c r="I7" t="n">
+        <v>555.4829</v>
+      </c>
+      <c r="J7" t="n">
+        <v>357.1867</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>380</v>
+      </c>
+      <c r="N7" t="n">
+        <v>824</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1943.4449</v>
+      </c>
+      <c r="P7" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.9931</v>
+      </c>
+      <c r="R7" t="n">
+        <v>214.1665</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8637</v>
+      </c>
+      <c r="T7" t="n">
+        <v>20090</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.04399676</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04101543</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.8016</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>311</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>599</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>424.9777</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>927.6245</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>6.2323</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3781</v>
+      </c>
+      <c r="C8" t="n">
+        <v>121.5015</v>
+      </c>
+      <c r="D8" t="n">
+        <v>43.6088</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.7862</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9334</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8771</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.4272</v>
+      </c>
+      <c r="I8" t="n">
+        <v>590.4819</v>
+      </c>
+      <c r="J8" t="n">
+        <v>55.0987</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>348</v>
+      </c>
+      <c r="N8" t="n">
+        <v>753</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1240.59</v>
+      </c>
+      <c r="P8" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>25.8456</v>
+      </c>
+      <c r="R8" t="n">
+        <v>322.8356</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9940</v>
+      </c>
+      <c r="T8" t="n">
+        <v>22198</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.8401999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7724</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.03501006</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.03392197</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.478</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>337</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>649</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>389.664</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>844.3402</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6.0784</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C9" t="n">
+        <v>81.52</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23.1918</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9587</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8541</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5542</v>
+      </c>
+      <c r="I9" t="n">
+        <v>716.1351</v>
+      </c>
+      <c r="J9" t="n">
+        <v>181.5704</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>263</v>
+      </c>
+      <c r="N9" t="n">
+        <v>717</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1262.0042</v>
+      </c>
+      <c r="P9" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>26.2918</v>
+      </c>
+      <c r="R9" t="n">
+        <v>229.4802</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8595</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22042</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.03059919</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.03252881</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.1788</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>126</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>186</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>289.5513</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>790.6417</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.681</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>513</v>
+      </c>
+      <c r="C10" t="n">
+        <v>41.8409</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17.3844</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.4068</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9096</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8607</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.3405</v>
+      </c>
+      <c r="I10" t="n">
+        <v>830.5653</v>
+      </c>
+      <c r="J10" t="n">
+        <v>75.58669999999999</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>133</v>
+      </c>
+      <c r="N10" t="n">
+        <v>421</v>
+      </c>
+      <c r="O10" t="n">
+        <v>419.6346</v>
+      </c>
+      <c r="P10" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23.313</v>
+      </c>
+      <c r="R10" t="n">
+        <v>109.4975</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4245</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11066</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.03133098</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.03804446</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.5663</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>119</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>296</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>148.1249</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>468.0193</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.633</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1130</v>
+      </c>
+      <c r="C11" t="n">
+        <v>64.3164</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23.6688</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.7173</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8835</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.4062</v>
+      </c>
+      <c r="I11" t="n">
+        <v>842.292</v>
+      </c>
+      <c r="J11" t="n">
+        <v>125.2372</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>155</v>
+      </c>
+      <c r="N11" t="n">
+        <v>438</v>
+      </c>
+      <c r="O11" t="n">
+        <v>476.8894</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>39.7408</v>
+      </c>
+      <c r="R11" t="n">
+        <v>161.8173</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5491</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13376</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.02822801</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.03274522</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.4719</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>133</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>298</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>180.0955</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>489.6762</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>7.0548</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1244</v>
+      </c>
+      <c r="C12" t="n">
+        <v>49.7173</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33.3792</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.4895</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9325</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.542</v>
+      </c>
+      <c r="I12" t="n">
+        <v>904.5997</v>
+      </c>
+      <c r="J12" t="n">
+        <v>760.8071</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>118</v>
+      </c>
+      <c r="N12" t="n">
+        <v>384</v>
+      </c>
+      <c r="O12" t="n">
+        <v>164.5807</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>18.2867</v>
+      </c>
+      <c r="R12" t="n">
+        <v>147.196</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6914</v>
+      </c>
+      <c r="T12" t="n">
+        <v>19480</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.01706682</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.01971253</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3587</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>137.4386</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>446.0732</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5.2457</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2966</v>
+      </c>
+      <c r="C13" t="n">
+        <v>92.1224</v>
+      </c>
+      <c r="D13" t="n">
+        <v>41.6334</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.2127</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8921</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.4899</v>
+      </c>
+      <c r="I13" t="n">
+        <v>920.4009</v>
+      </c>
+      <c r="J13" t="n">
+        <v>307.385</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>320</v>
+      </c>
+      <c r="N13" t="n">
+        <v>788</v>
+      </c>
+      <c r="O13" t="n">
+        <v>789.6123</v>
+      </c>
+      <c r="P13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>30.3697</v>
+      </c>
+      <c r="R13" t="n">
+        <v>254.6934</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9728</v>
+      </c>
+      <c r="T13" t="n">
+        <v>23664</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.03289474</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.03329953</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.7484</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>423</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>350.5929</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>873.997</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5.5407</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1624</v>
+      </c>
+      <c r="C14" t="n">
+        <v>72.5441</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29.7651</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.4372</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9119</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.945</v>
+      </c>
+      <c r="I14" t="n">
+        <v>978.4969</v>
+      </c>
+      <c r="J14" t="n">
+        <v>437.6151</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>188</v>
+      </c>
+      <c r="N14" t="n">
+        <v>351</v>
+      </c>
+      <c r="O14" t="n">
+        <v>294.4214</v>
+      </c>
+      <c r="P14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>21.0301</v>
+      </c>
+      <c r="R14" t="n">
+        <v>202.6934</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7711</v>
+      </c>
+      <c r="T14" t="n">
+        <v>16371</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.9376</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.02438075</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.02144035</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3.4535</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>135</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>211</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>206.6812</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>390.0193</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>6.2476</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3283,7 +3690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Measured only on skeleton pixels with real signal under them: bridged pixels, the lacuna buffer and the</t>
+          <t>Measured only on skeleton pixels on the canalicular mask: the lacuna buffer and the</t>
         </is>
       </c>
     </row>

--- a/results/682_z29/5_quantification/682_z29_quantification.xlsx
+++ b/results/682_z29/5_quantification/682_z29_quantification.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.3636</v>
+        <v>5.3333</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>1.804</v>
+        <v>2.9336</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>250.4545</v>
+        <v>271.3333</v>
       </c>
       <c r="D13" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E13" t="n">
-        <v>91.0136</v>
+        <v>112.7655</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>647.0909</v>
+        <v>719.5</v>
       </c>
       <c r="D14" t="n">
-        <v>696</v>
+        <v>745</v>
       </c>
       <c r="E14" t="n">
-        <v>247.374</v>
+        <v>289.7254</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1557.3019</v>
+        <v>1833.1525</v>
       </c>
       <c r="D15" t="n">
-        <v>1262.0042</v>
+        <v>1089.9148</v>
       </c>
       <c r="E15" t="n">
-        <v>1443.6751</v>
+        <v>1865.4025</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>65.9091</v>
+        <v>80.25</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>39.5</v>
       </c>
       <c r="E16" t="n">
-        <v>67.58620000000001</v>
+        <v>86.68980000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.2613</v>
+        <v>27.9834</v>
       </c>
       <c r="D17" t="n">
-        <v>23.9931</v>
+        <v>24.0785</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9707</v>
+        <v>9.060700000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>201.3086</v>
+        <v>188.4875</v>
       </c>
       <c r="D18" t="n">
-        <v>214.1665</v>
+        <v>208.43</v>
       </c>
       <c r="E18" t="n">
-        <v>60.6733</v>
+        <v>72.9325</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7938.5455</v>
+        <v>7625.9167</v>
       </c>
       <c r="D19" t="n">
-        <v>8595</v>
+        <v>8153</v>
       </c>
       <c r="E19" t="n">
-        <v>2078.1806</v>
+        <v>2258.1086</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19815</v>
+        <v>19043.3333</v>
       </c>
       <c r="D20" t="n">
-        <v>20090</v>
+        <v>19608.5</v>
       </c>
       <c r="E20" t="n">
-        <v>4945.8225</v>
+        <v>5099.6485</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9943</v>
+        <v>0.9948</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0188</v>
+        <v>0.018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.981</v>
+        <v>0.9826</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0583</v>
+        <v>0.0559</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0313798</v>
+        <v>0.03567298</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03133098</v>
+        <v>0.03467746</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00760002</v>
+        <v>0.01089529</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03234375</v>
+        <v>0.03762232</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03274522</v>
+        <v>0.03833529</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00701619</v>
+        <v>0.00985305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7581</v>
+        <v>2.8718</v>
       </c>
       <c r="D25" t="n">
-        <v>2.7484</v>
+        <v>2.437</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9127</v>
+        <v>1.3562</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>186.9091</v>
+        <v>202.1667</v>
       </c>
       <c r="D26" t="n">
-        <v>160</v>
+        <v>175.5</v>
       </c>
       <c r="E26" t="n">
-        <v>84.6953</v>
+        <v>115.3649</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>401.6364</v>
+        <v>470.0833</v>
       </c>
       <c r="D27" t="n">
-        <v>334</v>
+        <v>338.5</v>
       </c>
       <c r="E27" t="n">
-        <v>227.1824</v>
+        <v>350.8668</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>277.945</v>
+        <v>302.0262</v>
       </c>
       <c r="D28" t="n">
-        <v>289.5513</v>
+        <v>307.1015</v>
       </c>
       <c r="E28" t="n">
-        <v>98.9509</v>
+        <v>123.4519</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>723.2128</v>
+        <v>805.3094</v>
       </c>
       <c r="D29" t="n">
-        <v>790.6417</v>
+        <v>825.9909</v>
       </c>
       <c r="E29" t="n">
-        <v>273.2569</v>
+        <v>323.8226</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.2727</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>2.149</v>
+        <v>2.8284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.2727</v>
+        <v>9.333299999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="E31" t="n">
-        <v>3.6631</v>
+        <v>3.8218</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10.2727</v>
+        <v>11.1667</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E32" t="n">
-        <v>3.7707</v>
+        <v>3.9505</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.9497</v>
+        <v>6.9667</v>
       </c>
       <c r="D33" t="n">
-        <v>6.2323</v>
+        <v>7.0528</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6796</v>
+        <v>0.8127</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1023566</v>
+        <v>1023391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29332</v>
+        <v>33508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02865668</v>
+        <v>0.03274213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>537</v>
+        <v>674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00052464</v>
+        <v>0.00065859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.27e-05</v>
+        <v>1.368e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>101.4948</v>
+        <v>126.4453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03240016</v>
+        <v>0.03700763</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02970713</v>
+        <v>0.03305751</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>513</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03274213</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0332434</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.7771</v>
+        <v>7.4342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28159</v>
+        <v>31329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1889,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>420</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.677</v>
+        <v>22.1385</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4385</v>
+        <v>0.4438</v>
       </c>
     </row>
     <row r="11">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44.4749</v>
+        <v>46.9558</v>
       </c>
     </row>
     <row r="12">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3929</v>
+        <v>0.4507</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6071</v>
+        <v>0.5493</v>
       </c>
     </row>
     <row r="15">
@@ -2026,7 +2106,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9374</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="25">
@@ -2179,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>128</v>
@@ -2393,13 +2473,13 @@
         <v>230</v>
       </c>
       <c r="O2" t="n">
-        <v>20.4853</v>
+        <v>90.84059999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.4853</v>
+        <v>11.3551</v>
       </c>
       <c r="R2" t="n">
         <v>262.0955</v>
@@ -2423,7 +2503,7 @@
         <v>0.01664375</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3815</v>
+        <v>1.1446</v>
       </c>
       <c r="Z2" t="n">
         <v>20</v>
@@ -2482,22 +2562,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>310</v>
+        <v>463</v>
       </c>
       <c r="N3" t="n">
-        <v>696</v>
+        <v>1191</v>
       </c>
       <c r="O3" t="n">
-        <v>2661.2237</v>
+        <v>4157.7964</v>
       </c>
       <c r="P3" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.1929</v>
+        <v>21.8831</v>
       </c>
       <c r="R3" t="n">
         <v>229.5219</v>
@@ -2515,37 +2595,37 @@
         <v>0.999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03387608</v>
+        <v>0.05059556</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02915672</v>
+        <v>0.04989318</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.4855</v>
+        <v>4.3569</v>
       </c>
       <c r="Z3" t="n">
-        <v>259</v>
+        <v>377</v>
       </c>
       <c r="AA3" t="n">
-        <v>574</v>
+        <v>1057</v>
       </c>
       <c r="AB3" t="n">
-        <v>340.1076</v>
+        <v>509.5341</v>
       </c>
       <c r="AC3" t="n">
-        <v>791.0681</v>
+        <v>1347.5017</v>
       </c>
       <c r="AD3" t="n">
         <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.5551</v>
+        <v>7.0028</v>
       </c>
     </row>
     <row r="4">
@@ -2583,22 +2663,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>263</v>
+        <v>347</v>
       </c>
       <c r="N4" t="n">
-        <v>566</v>
+        <v>918</v>
       </c>
       <c r="O4" t="n">
-        <v>2166.4154</v>
+        <v>5123.5537</v>
       </c>
       <c r="P4" t="n">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.6325</v>
+        <v>21.9895</v>
       </c>
       <c r="R4" t="n">
         <v>120.8112</v>
@@ -2616,37 +2696,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04287577</v>
+        <v>0.05656994</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03160069</v>
+        <v>0.05125342</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.311</v>
+        <v>4.1387</v>
       </c>
       <c r="Z4" t="n">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="AA4" t="n">
-        <v>557</v>
+        <v>902</v>
       </c>
       <c r="AB4" t="n">
-        <v>298.3797</v>
+        <v>390.0782</v>
       </c>
       <c r="AC4" t="n">
-        <v>640.4874</v>
+        <v>1018.3402</v>
       </c>
       <c r="AD4" t="n">
         <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AF4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.3915</v>
+        <v>7.4637</v>
       </c>
     </row>
     <row r="5">
@@ -2684,22 +2764,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="N5" t="n">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="O5" t="n">
-        <v>5067.8035</v>
+        <v>4365.2501</v>
       </c>
       <c r="P5" t="n">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.4737</v>
+        <v>21.1905</v>
       </c>
       <c r="R5" t="n">
         <v>309.2792</v>
@@ -2708,7 +2788,7 @@
         <v>11331</v>
       </c>
       <c r="T5" t="n">
-        <v>28206</v>
+        <v>27269</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
@@ -2717,28 +2797,28 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03212426</v>
+        <v>0.03468361</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04183507</v>
+        <v>0.04371264</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2633</v>
+        <v>1.94</v>
       </c>
       <c r="Z5" t="n">
-        <v>290</v>
+        <v>353</v>
       </c>
       <c r="AA5" t="n">
-        <v>860</v>
+        <v>1007</v>
       </c>
       <c r="AB5" t="n">
-        <v>401.8356</v>
+        <v>437.6346</v>
       </c>
       <c r="AC5" t="n">
-        <v>1313.5483</v>
+        <v>1335.4478</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
@@ -2747,7 +2827,7 @@
         <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.3155</v>
+        <v>7.5622</v>
       </c>
     </row>
     <row r="6">
@@ -2785,22 +2865,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="N6" t="n">
-        <v>753</v>
+        <v>796</v>
       </c>
       <c r="O6" t="n">
-        <v>1884.2905</v>
+        <v>2413.5525</v>
       </c>
       <c r="P6" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.5499</v>
+        <v>24.1355</v>
       </c>
       <c r="R6" t="n">
         <v>235.2376</v>
@@ -2818,25 +2898,25 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02780441</v>
+        <v>0.02855012</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03440241</v>
+        <v>0.03636696</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7004</v>
+        <v>2.1255</v>
       </c>
       <c r="Z6" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="AA6" t="n">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="AB6" t="n">
-        <v>279.6102</v>
+        <v>292.0955</v>
       </c>
       <c r="AC6" t="n">
-        <v>824.1858999999999</v>
+        <v>878.7422</v>
       </c>
       <c r="AD6" t="n">
         <v>5</v>
@@ -2848,7 +2928,7 @@
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.5492</v>
+        <v>6.8365</v>
       </c>
     </row>
     <row r="7">
@@ -2886,22 +2966,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="N7" t="n">
-        <v>824</v>
+        <v>858</v>
       </c>
       <c r="O7" t="n">
-        <v>1943.4449</v>
+        <v>2668.2876</v>
       </c>
       <c r="P7" t="n">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.9931</v>
+        <v>23.2025</v>
       </c>
       <c r="R7" t="n">
         <v>214.1665</v>
@@ -2910,7 +2990,7 @@
         <v>8637</v>
       </c>
       <c r="T7" t="n">
-        <v>20090</v>
+        <v>19737</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -2919,37 +2999,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04399676</v>
+        <v>0.04561769</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04101543</v>
+        <v>0.04347165</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.8016</v>
+        <v>3.2685</v>
       </c>
       <c r="Z7" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AA7" t="n">
-        <v>599</v>
+        <v>662</v>
       </c>
       <c r="AB7" t="n">
-        <v>424.9777</v>
+        <v>437.9777</v>
       </c>
       <c r="AC7" t="n">
-        <v>927.6245</v>
+        <v>959.9675999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.2323</v>
+        <v>7.3633</v>
       </c>
     </row>
     <row r="8">
@@ -2987,22 +3067,22 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="N8" t="n">
-        <v>753</v>
+        <v>783</v>
       </c>
       <c r="O8" t="n">
-        <v>1240.59</v>
+        <v>1341.7027</v>
       </c>
       <c r="P8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.8456</v>
+        <v>24.3946</v>
       </c>
       <c r="R8" t="n">
         <v>322.8356</v>
@@ -3011,7 +3091,7 @@
         <v>9940</v>
       </c>
       <c r="T8" t="n">
-        <v>22198</v>
+        <v>21386</v>
       </c>
       <c r="U8" t="n">
         <v>0.8401999999999999</v>
@@ -3020,25 +3100,25 @@
         <v>0.7724</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03501006</v>
+        <v>0.03631791</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03392197</v>
+        <v>0.03661274</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.478</v>
+        <v>2.7878</v>
       </c>
       <c r="Z8" t="n">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="AA8" t="n">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="AB8" t="n">
-        <v>389.664</v>
+        <v>404.4924</v>
       </c>
       <c r="AC8" t="n">
-        <v>844.3402</v>
+        <v>880.997</v>
       </c>
       <c r="AD8" t="n">
         <v>10</v>
@@ -3047,10 +3127,10 @@
         <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.0784</v>
+        <v>7.473</v>
       </c>
     </row>
     <row r="9">
@@ -3088,22 +3168,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="N9" t="n">
-        <v>717</v>
+        <v>758</v>
       </c>
       <c r="O9" t="n">
-        <v>1262.0042</v>
+        <v>1507.2296</v>
       </c>
       <c r="P9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.2918</v>
+        <v>29.5535</v>
       </c>
       <c r="R9" t="n">
         <v>229.4802</v>
@@ -3121,37 +3201,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03059919</v>
+        <v>0.03467132</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03252881</v>
+        <v>0.03438889</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1788</v>
+        <v>1.7431</v>
       </c>
       <c r="Z9" t="n">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="AA9" t="n">
-        <v>186</v>
+        <v>261</v>
       </c>
       <c r="AB9" t="n">
-        <v>289.5513</v>
+        <v>328.2082</v>
       </c>
       <c r="AC9" t="n">
-        <v>790.6417</v>
+        <v>836.127</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.681</v>
+        <v>5.2862</v>
       </c>
     </row>
     <row r="10">
@@ -3192,19 +3272,19 @@
         <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="N10" t="n">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="O10" t="n">
-        <v>419.6346</v>
+        <v>314.4508</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.313</v>
+        <v>28.5864</v>
       </c>
       <c r="R10" t="n">
         <v>109.4975</v>
@@ -3222,25 +3302,25 @@
         <v>0.9865</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03133098</v>
+        <v>0.03651355</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03804446</v>
+        <v>0.04030363</v>
       </c>
       <c r="Y10" t="n">
         <v>4.5663</v>
       </c>
       <c r="Z10" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="AA10" t="n">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="AB10" t="n">
-        <v>148.1249</v>
+        <v>173.0244</v>
       </c>
       <c r="AC10" t="n">
-        <v>468.0193</v>
+        <v>496.333</v>
       </c>
       <c r="AD10" t="n">
         <v>6</v>
@@ -3252,7 +3332,7 @@
         <v>5</v>
       </c>
       <c r="AG10" t="n">
-        <v>5.633</v>
+        <v>6.8163</v>
       </c>
     </row>
     <row r="11">
@@ -3290,22 +3370,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
         <v>155</v>
       </c>
       <c r="N11" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O11" t="n">
-        <v>476.8894</v>
+        <v>340.1493</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.7408</v>
+        <v>34.0149</v>
       </c>
       <c r="R11" t="n">
         <v>161.8173</v>
@@ -3326,22 +3406,22 @@
         <v>0.02822801</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03274522</v>
+        <v>0.03281998</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.4719</v>
+        <v>1.8539</v>
       </c>
       <c r="Z11" t="n">
         <v>133</v>
       </c>
       <c r="AA11" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AB11" t="n">
-        <v>180.0955</v>
+        <v>179.6812</v>
       </c>
       <c r="AC11" t="n">
-        <v>489.6762</v>
+        <v>491.0904</v>
       </c>
       <c r="AD11" t="n">
         <v>4</v>
@@ -3353,7 +3433,7 @@
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.0548</v>
+        <v>7.9932</v>
       </c>
     </row>
     <row r="12">
@@ -3391,22 +3471,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>118</v>
       </c>
       <c r="N12" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="O12" t="n">
-        <v>164.5807</v>
+        <v>52.3553</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>18.2867</v>
+        <v>52.3553</v>
       </c>
       <c r="R12" t="n">
         <v>147.196</v>
@@ -3427,22 +3507,22 @@
         <v>0.01706682</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01971253</v>
+        <v>0.0199692</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3587</v>
+        <v>0.6794</v>
       </c>
       <c r="Z12" t="n">
         <v>46</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="AB12" t="n">
-        <v>137.4386</v>
+        <v>136.196</v>
       </c>
       <c r="AC12" t="n">
-        <v>446.0732</v>
+        <v>452.0732</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
@@ -3454,7 +3534,7 @@
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.2457</v>
+        <v>5.5177</v>
       </c>
     </row>
     <row r="13">
@@ -3495,19 +3575,19 @@
         <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="N13" t="n">
-        <v>788</v>
+        <v>732</v>
       </c>
       <c r="O13" t="n">
-        <v>789.6123</v>
+        <v>672.6001</v>
       </c>
       <c r="P13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="n">
-        <v>30.3697</v>
+        <v>24.0214</v>
       </c>
       <c r="R13" t="n">
         <v>254.6934</v>
@@ -3525,37 +3605,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03289474</v>
+        <v>0.02981086</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03329953</v>
+        <v>0.03093306</v>
       </c>
       <c r="Y13" t="n">
         <v>2.7484</v>
       </c>
       <c r="Z13" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AA13" t="n">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="AB13" t="n">
-        <v>350.5929</v>
+        <v>322.1076</v>
       </c>
       <c r="AC13" t="n">
-        <v>873.997</v>
+        <v>815.8549</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.5407</v>
+        <v>7.0222</v>
       </c>
     </row>
     <row r="14">
@@ -3593,22 +3673,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="N14" t="n">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="O14" t="n">
-        <v>294.4214</v>
+        <v>348.2203</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.0301</v>
+        <v>20.4835</v>
       </c>
       <c r="R14" t="n">
         <v>202.6934</v>
@@ -3626,37 +3706,117 @@
         <v>0.8055</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02438075</v>
+        <v>0.0282713</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02144035</v>
+        <v>0.02327286</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4535</v>
+        <v>4.9336</v>
       </c>
       <c r="Z14" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="AA14" t="n">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="AB14" t="n">
-        <v>206.6812</v>
+        <v>242.8944</v>
       </c>
       <c r="AC14" t="n">
-        <v>390.0193</v>
+        <v>425.4041</v>
       </c>
       <c r="AD14" t="n">
         <v>6</v>
       </c>
       <c r="AE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>7.0835</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>548.08</v>
+      </c>
+      <c r="J15" t="n">
+        <v>212.6629</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>157</v>
+      </c>
+      <c r="N15" t="n">
+        <v>534</v>
+      </c>
+      <c r="O15" t="n">
+        <v>34.3848</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>34.3848</v>
+      </c>
+      <c r="R15" t="n">
+        <v>47.4558</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4187</v>
+      </c>
+      <c r="T15" t="n">
+        <v>11845</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.03749701</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.04508231</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.1072</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>174.8823</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>606.8305</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
         <v>5</v>
       </c>
-      <c r="AF14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>6.2476</v>
+      <c r="AF15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>7.6531</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z29/5_quantification/682_z29_quantification.xlsx
+++ b/results/682_z29/5_quantification/682_z29_quantification.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1740.5455</v>
+        <v>1650.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1624</v>
+        <v>1511.5</v>
       </c>
       <c r="E6" t="n">
-        <v>939.6417</v>
+        <v>948.3771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75.1181</v>
+        <v>74.0009</v>
       </c>
       <c r="D7" t="n">
-        <v>75.9278</v>
+        <v>74.236</v>
       </c>
       <c r="E7" t="n">
-        <v>23.0542</v>
+        <v>22.3194</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.0371</v>
+        <v>27.9394</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0551</v>
+        <v>29.9101</v>
       </c>
       <c r="E8" t="n">
-        <v>9.235900000000001</v>
+        <v>9.591900000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.7064</v>
+        <v>2.805</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5263</v>
+        <v>2.6218</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7296</v>
+        <v>0.775</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9096</v>
+        <v>0.9144</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9183</v>
+        <v>0.9241</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0622</v>
+        <v>0.0615</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.87</v>
+        <v>0.8593</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8778</v>
+        <v>0.8693</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0425</v>
+        <v>0.0551</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.3333</v>
+        <v>5.4615</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9336</v>
+        <v>2.8465</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>271.3333</v>
+        <v>263.9231</v>
       </c>
       <c r="D13" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E13" t="n">
-        <v>112.7655</v>
+        <v>111.265</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>719.5</v>
+        <v>707</v>
       </c>
       <c r="D14" t="n">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="E14" t="n">
-        <v>289.7254</v>
+        <v>280.7867</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1833.1525</v>
+        <v>1882.4861</v>
       </c>
       <c r="D15" t="n">
-        <v>1089.9148</v>
+        <v>1507.2296</v>
       </c>
       <c r="E15" t="n">
-        <v>1865.4025</v>
+        <v>1794.8227</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>80.25</v>
+        <v>81.61539999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>39.5</v>
+        <v>51</v>
       </c>
       <c r="E16" t="n">
-        <v>86.68980000000001</v>
+        <v>83.145</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.9834</v>
+        <v>27.7731</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0785</v>
+        <v>24.1355</v>
       </c>
       <c r="E17" t="n">
-        <v>9.060700000000001</v>
+        <v>8.7081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>188.4875</v>
+        <v>186.0541</v>
       </c>
       <c r="D18" t="n">
-        <v>208.43</v>
+        <v>202.6934</v>
       </c>
       <c r="E18" t="n">
-        <v>72.9325</v>
+        <v>70.3766</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7625.9167</v>
+        <v>7571.7692</v>
       </c>
       <c r="D19" t="n">
-        <v>8153</v>
+        <v>7711</v>
       </c>
       <c r="E19" t="n">
-        <v>2258.1086</v>
+        <v>2170.7714</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19043.3333</v>
+        <v>19073</v>
       </c>
       <c r="D20" t="n">
-        <v>19608.5</v>
+        <v>19480</v>
       </c>
       <c r="E20" t="n">
-        <v>5099.6485</v>
+        <v>4883.7132</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9948</v>
+        <v>0.9952</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.018</v>
+        <v>0.0173</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9826</v>
+        <v>0.9839</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0559</v>
+        <v>0.0537</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03567298</v>
+        <v>0.03487364</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03467746</v>
+        <v>0.03467132</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01089529</v>
+        <v>0.01083157</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03762232</v>
+        <v>0.03693351</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03833529</v>
+        <v>0.03636696</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00985305</v>
+        <v>0.00973648</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.8718</v>
+        <v>2.9942</v>
       </c>
       <c r="D25" t="n">
-        <v>2.437</v>
+        <v>2.7484</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3562</v>
+        <v>1.3714</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>202.1667</v>
+        <v>198.8462</v>
       </c>
       <c r="D26" t="n">
-        <v>175.5</v>
+        <v>170</v>
       </c>
       <c r="E26" t="n">
-        <v>115.3649</v>
+        <v>111.1004</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>470.0833</v>
+        <v>463</v>
       </c>
       <c r="D27" t="n">
-        <v>338.5</v>
+        <v>356</v>
       </c>
       <c r="E27" t="n">
-        <v>350.8668</v>
+        <v>336.8988</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>302.0262</v>
+        <v>294.7215</v>
       </c>
       <c r="D28" t="n">
-        <v>307.1015</v>
+        <v>292.0955</v>
       </c>
       <c r="E28" t="n">
-        <v>123.4519</v>
+        <v>121.1653</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>805.3094</v>
+        <v>793.1523999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>825.9909</v>
+        <v>815.8549</v>
       </c>
       <c r="E29" t="n">
-        <v>323.8226</v>
+        <v>312.916</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>5.9231</v>
       </c>
       <c r="D30" t="n">
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8284</v>
+        <v>2.7222</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.333299999999999</v>
+        <v>9.1538</v>
       </c>
       <c r="D31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>3.8218</v>
+        <v>3.7159</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.1667</v>
+        <v>10.9231</v>
       </c>
       <c r="D32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9505</v>
+        <v>3.8829</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.9667</v>
+        <v>6.9859</v>
       </c>
       <c r="D33" t="n">
-        <v>7.0528</v>
+        <v>7.0222</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8127</v>
+        <v>0.7395</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1023391</v>
+        <v>1022728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33508</v>
+        <v>33573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03274213</v>
+        <v>0.03282691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00065859</v>
+        <v>0.00066489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.368e-05</v>
+        <v>1.467e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>126.4453</v>
+        <v>128.1412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03700763</v>
+        <v>0.03708711</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03305751</v>
+        <v>0.03314929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03274213</v>
+        <v>0.03282691</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0332434</v>
+        <v>0.03332851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.4342</v>
+        <v>7.5051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31329</v>
+        <v>31394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>497</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.1385</v>
+        <v>21.9678</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.9558</v>
+        <v>46.4029</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4507</v>
+        <v>0.4474</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5493</v>
+        <v>0.5526</v>
       </c>
     </row>
     <row r="15">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2259,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3239,100 +3239,100 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>513</v>
+        <v>663</v>
       </c>
       <c r="C10" t="n">
-        <v>41.8409</v>
+        <v>61.7115</v>
       </c>
       <c r="D10" t="n">
-        <v>17.3844</v>
+        <v>15.8655</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4068</v>
+        <v>3.8897</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9096</v>
+        <v>0.9664</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8607</v>
+        <v>0.7408</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3405</v>
+        <v>-1.1603</v>
       </c>
       <c r="I10" t="n">
-        <v>830.5653</v>
+        <v>728.5958000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>75.58669999999999</v>
+        <v>861.0603</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="N10" t="n">
-        <v>446</v>
+        <v>552</v>
       </c>
       <c r="O10" t="n">
-        <v>314.4508</v>
+        <v>2474.4886</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.5864</v>
+        <v>25.2499</v>
       </c>
       <c r="R10" t="n">
-        <v>109.4975</v>
+        <v>156.8528</v>
       </c>
       <c r="S10" t="n">
-        <v>4245</v>
+        <v>6922</v>
       </c>
       <c r="T10" t="n">
-        <v>11066</v>
+        <v>19429</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9865</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03651355</v>
+        <v>0.02542618</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04030363</v>
+        <v>0.02841114</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.5663</v>
+        <v>4.4628</v>
       </c>
       <c r="Z10" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="AA10" t="n">
-        <v>321</v>
+        <v>378</v>
       </c>
       <c r="AB10" t="n">
-        <v>173.0244</v>
+        <v>208.4802</v>
       </c>
       <c r="AC10" t="n">
-        <v>496.333</v>
+        <v>643.2691</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.8163</v>
+        <v>6.9506</v>
       </c>
     </row>
     <row r="11">
@@ -3340,100 +3340,100 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1130</v>
+        <v>513</v>
       </c>
       <c r="C11" t="n">
-        <v>64.3164</v>
+        <v>41.8409</v>
       </c>
       <c r="D11" t="n">
-        <v>23.6688</v>
+        <v>17.3844</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7173</v>
+        <v>2.4068</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9298</v>
+        <v>0.9096</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8835</v>
+        <v>0.8607</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4062</v>
+        <v>1.3405</v>
       </c>
       <c r="I11" t="n">
-        <v>842.292</v>
+        <v>830.5653</v>
       </c>
       <c r="J11" t="n">
-        <v>125.2372</v>
+        <v>75.58669999999999</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
         <v>155</v>
       </c>
       <c r="N11" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="O11" t="n">
-        <v>340.1493</v>
+        <v>314.4508</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>34.0149</v>
+        <v>28.5864</v>
       </c>
       <c r="R11" t="n">
-        <v>161.8173</v>
+        <v>109.4975</v>
       </c>
       <c r="S11" t="n">
-        <v>5491</v>
+        <v>4245</v>
       </c>
       <c r="T11" t="n">
-        <v>13376</v>
+        <v>11066</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0.9865</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02822801</v>
+        <v>0.03651355</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03281998</v>
+        <v>0.04030363</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8539</v>
+        <v>4.5663</v>
       </c>
       <c r="Z11" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AA11" t="n">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="AB11" t="n">
-        <v>179.6812</v>
+        <v>173.0244</v>
       </c>
       <c r="AC11" t="n">
-        <v>491.0904</v>
+        <v>496.333</v>
       </c>
       <c r="AD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE11" t="n">
         <v>4</v>
       </c>
-      <c r="AE11" t="n">
-        <v>7</v>
-      </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.9932</v>
+        <v>6.8163</v>
       </c>
     </row>
     <row r="12">
@@ -3441,61 +3441,61 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1244</v>
+        <v>1130</v>
       </c>
       <c r="C12" t="n">
-        <v>49.7173</v>
+        <v>64.3164</v>
       </c>
       <c r="D12" t="n">
-        <v>33.3792</v>
+        <v>23.6688</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4895</v>
+        <v>2.7173</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7411</v>
+        <v>0.9298</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9325</v>
+        <v>0.8835</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.542</v>
+        <v>1.4062</v>
       </c>
       <c r="I12" t="n">
-        <v>904.5997</v>
+        <v>842.292</v>
       </c>
       <c r="J12" t="n">
-        <v>760.8071</v>
+        <v>125.2372</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="N12" t="n">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="O12" t="n">
-        <v>52.3553</v>
+        <v>340.1493</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.3553</v>
+        <v>34.0149</v>
       </c>
       <c r="R12" t="n">
-        <v>147.196</v>
+        <v>161.8173</v>
       </c>
       <c r="S12" t="n">
-        <v>6914</v>
+        <v>5491</v>
       </c>
       <c r="T12" t="n">
-        <v>19480</v>
+        <v>13376</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -3504,37 +3504,37 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01706682</v>
+        <v>0.02822801</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0199692</v>
+        <v>0.03281998</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6794</v>
+        <v>1.8539</v>
       </c>
       <c r="Z12" t="n">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="AA12" t="n">
-        <v>96</v>
+        <v>299</v>
       </c>
       <c r="AB12" t="n">
-        <v>136.196</v>
+        <v>179.6812</v>
       </c>
       <c r="AC12" t="n">
-        <v>452.0732</v>
+        <v>491.0904</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.5177</v>
+        <v>7.9932</v>
       </c>
     </row>
     <row r="13">
@@ -3542,61 +3542,61 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2966</v>
+        <v>1244</v>
       </c>
       <c r="C13" t="n">
-        <v>92.1224</v>
+        <v>49.7173</v>
       </c>
       <c r="D13" t="n">
-        <v>41.6334</v>
+        <v>33.3792</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2127</v>
+        <v>1.4895</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8921</v>
+        <v>0.7411</v>
       </c>
       <c r="G13" t="n">
-        <v>0.895</v>
+        <v>0.9325</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4899</v>
+        <v>-1.542</v>
       </c>
       <c r="I13" t="n">
-        <v>920.4009</v>
+        <v>904.5997</v>
       </c>
       <c r="J13" t="n">
-        <v>307.385</v>
+        <v>760.8071</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>290</v>
+        <v>117</v>
       </c>
       <c r="N13" t="n">
-        <v>732</v>
+        <v>394</v>
       </c>
       <c r="O13" t="n">
-        <v>672.6001</v>
+        <v>52.3553</v>
       </c>
       <c r="P13" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.0214</v>
+        <v>52.3553</v>
       </c>
       <c r="R13" t="n">
-        <v>254.6934</v>
+        <v>147.196</v>
       </c>
       <c r="S13" t="n">
-        <v>9728</v>
+        <v>6914</v>
       </c>
       <c r="T13" t="n">
-        <v>23664</v>
+        <v>19480</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
@@ -3605,37 +3605,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02981086</v>
+        <v>0.01692219</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03093306</v>
+        <v>0.02022587</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.7484</v>
+        <v>0.6794</v>
       </c>
       <c r="Z13" t="n">
-        <v>213</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>409</v>
+        <v>96</v>
       </c>
       <c r="AB13" t="n">
-        <v>322.1076</v>
+        <v>134.7817</v>
       </c>
       <c r="AC13" t="n">
-        <v>815.8549</v>
+        <v>456.0732</v>
       </c>
       <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="n">
         <v>5</v>
       </c>
-      <c r="AE13" t="n">
-        <v>10</v>
-      </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>7.0222</v>
+        <v>5.7831</v>
       </c>
     </row>
     <row r="14">
@@ -3643,179 +3643,280 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1624</v>
+        <v>2966</v>
       </c>
       <c r="C14" t="n">
-        <v>72.5441</v>
+        <v>92.1224</v>
       </c>
       <c r="D14" t="n">
-        <v>29.7651</v>
+        <v>41.6334</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4372</v>
+        <v>2.2127</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9119</v>
+        <v>0.8921</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8476</v>
+        <v>0.895</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.945</v>
+        <v>-1.4899</v>
       </c>
       <c r="I14" t="n">
-        <v>978.4969</v>
+        <v>920.4009</v>
       </c>
       <c r="J14" t="n">
-        <v>437.6151</v>
+        <v>307.385</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>290</v>
+      </c>
+      <c r="N14" t="n">
+        <v>732</v>
+      </c>
+      <c r="O14" t="n">
+        <v>672.6001</v>
+      </c>
+      <c r="P14" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>24.0214</v>
+      </c>
+      <c r="R14" t="n">
+        <v>254.6934</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9728</v>
+      </c>
+      <c r="T14" t="n">
+        <v>23664</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.02981086</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.03093306</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.7484</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>213</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>409</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>322.1076</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>815.8549</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE14" t="n">
         <v>10</v>
       </c>
-      <c r="M14" t="n">
-        <v>218</v>
-      </c>
-      <c r="N14" t="n">
-        <v>381</v>
-      </c>
-      <c r="O14" t="n">
-        <v>348.2203</v>
-      </c>
-      <c r="P14" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>20.4835</v>
-      </c>
-      <c r="R14" t="n">
-        <v>202.6934</v>
-      </c>
-      <c r="S14" t="n">
-        <v>7711</v>
-      </c>
-      <c r="T14" t="n">
-        <v>16371</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.9376</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.8055</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.0282713</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.02327286</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>4.9336</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>181</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>241</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>242.8944</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>425.4041</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>6</v>
-      </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.0835</v>
+        <v>7.0222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
+      <c r="B15" t="n">
+        <v>1624</v>
+      </c>
+      <c r="C15" t="n">
+        <v>72.5441</v>
+      </c>
+      <c r="D15" t="n">
+        <v>29.7651</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.4372</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9119</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.945</v>
+      </c>
       <c r="I15" t="n">
-        <v>548.08</v>
+        <v>978.4969</v>
       </c>
       <c r="J15" t="n">
-        <v>212.6629</v>
+        <v>437.6151</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" t="n">
+        <v>218</v>
+      </c>
+      <c r="N15" t="n">
+        <v>381</v>
+      </c>
+      <c r="O15" t="n">
+        <v>348.2203</v>
+      </c>
+      <c r="P15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>20.4835</v>
+      </c>
+      <c r="R15" t="n">
+        <v>202.6934</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7711</v>
+      </c>
+      <c r="T15" t="n">
+        <v>16371</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.9376</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.0282713</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.02327286</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.9336</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>181</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>241</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>242.8944</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>425.4041</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>7.0835</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>548.08</v>
+      </c>
+      <c r="J16" t="n">
+        <v>212.6629</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>157</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>534</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O16" t="n">
         <v>34.3848</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
         <v>34.3848</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>47.4558</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>4187</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>11845</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V16" t="n">
         <v>1</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W16" t="n">
         <v>0.03749701</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X16" t="n">
         <v>0.04508231</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y16" t="n">
         <v>2.1072</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z16" t="n">
         <v>21</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA16" t="n">
         <v>30</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB16" t="n">
         <v>174.8823</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC16" t="n">
         <v>606.8305</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD16" t="n">
         <v>1</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE16" t="n">
         <v>5</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AF16" t="n">
         <v>10</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG16" t="n">
         <v>7.6531</v>
       </c>
     </row>

--- a/results/682_z29/5_quantification/682_z29_quantification.xlsx
+++ b/results/682_z29/5_quantification/682_z29_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.4615</v>
+        <v>6.1538</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8465</v>
+        <v>2.9678</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>263.9231</v>
+        <v>264.5385</v>
       </c>
       <c r="D13" t="n">
         <v>268</v>
       </c>
       <c r="E13" t="n">
-        <v>111.265</v>
+        <v>111.0117</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>707</v>
+        <v>708.9231</v>
       </c>
       <c r="D14" t="n">
         <v>732</v>
       </c>
       <c r="E14" t="n">
-        <v>280.7867</v>
+        <v>280.6642</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1882.4861</v>
+        <v>1905.5153</v>
       </c>
       <c r="D15" t="n">
-        <v>1507.2296</v>
+        <v>1513.8154</v>
       </c>
       <c r="E15" t="n">
-        <v>1794.8227</v>
+        <v>1766.7778</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>81.61539999999999</v>
+        <v>82.5385</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>83.145</v>
+        <v>82.2259</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.7731</v>
+        <v>27.8208</v>
       </c>
       <c r="D17" t="n">
-        <v>24.1355</v>
+        <v>24.294</v>
       </c>
       <c r="E17" t="n">
-        <v>8.7081</v>
+        <v>9.0184</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03487364</v>
+        <v>0.0349763</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03467132</v>
+        <v>0.03468361</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01083157</v>
+        <v>0.01081229</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03693351</v>
+        <v>0.03703612</v>
       </c>
       <c r="D24" t="n">
         <v>0.03636696</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00973648</v>
+        <v>0.009710369999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.9942</v>
+        <v>3.3705</v>
       </c>
       <c r="D25" t="n">
-        <v>2.7484</v>
+        <v>3.0504</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3714</v>
+        <v>1.5392</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>198.8462</v>
+        <v>200.0769</v>
       </c>
       <c r="D26" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E26" t="n">
-        <v>111.1004</v>
+        <v>110.6047</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>463</v>
+        <v>464.6154</v>
       </c>
       <c r="D27" t="n">
         <v>356</v>
       </c>
       <c r="E27" t="n">
-        <v>336.8988</v>
+        <v>336.1097</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>294.7215</v>
+        <v>295.3183</v>
       </c>
       <c r="D28" t="n">
         <v>292.0955</v>
       </c>
       <c r="E28" t="n">
-        <v>121.1653</v>
+        <v>120.9282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>793.1523999999999</v>
+        <v>795.5107</v>
       </c>
       <c r="D29" t="n">
         <v>815.8549</v>
       </c>
       <c r="E29" t="n">
-        <v>312.916</v>
+        <v>312.688</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.9859</v>
+        <v>7.0539</v>
       </c>
       <c r="D33" t="n">
         <v>7.0222</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7395</v>
+        <v>0.6399</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33573</v>
+        <v>33616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03282691</v>
+        <v>0.03286895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00066489</v>
+        <v>0.00066782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>128.1412</v>
+        <v>129.2923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03708711</v>
+        <v>0.03713687</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03314929</v>
+        <v>0.03319469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03282691</v>
+        <v>0.03286895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03332851</v>
+        <v>0.03337055</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.5051</v>
+        <v>7.516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31394</v>
+        <v>31437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
         <v>393</v>
@@ -2803,7 +2803,7 @@
         <v>0.04371264</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.94</v>
+        <v>2.5867</v>
       </c>
       <c r="Z5" t="n">
         <v>353</v>
@@ -2975,13 +2975,13 @@
         <v>858</v>
       </c>
       <c r="O7" t="n">
-        <v>2668.2876</v>
+        <v>2568.1038</v>
       </c>
       <c r="P7" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.2025</v>
+        <v>22.7266</v>
       </c>
       <c r="R7" t="n">
         <v>214.1665</v>
@@ -3067,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>361</v>
@@ -3106,7 +3106,7 @@
         <v>0.03661274</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.7878</v>
+        <v>3.7171</v>
       </c>
       <c r="Z8" t="n">
         <v>350</v>
@@ -3168,22 +3168,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N9" t="n">
-        <v>758</v>
+        <v>777</v>
       </c>
       <c r="O9" t="n">
-        <v>1507.2296</v>
+        <v>1513.8154</v>
       </c>
       <c r="P9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q9" t="n">
-        <v>29.5535</v>
+        <v>29.1118</v>
       </c>
       <c r="R9" t="n">
         <v>229.4802</v>
@@ -3201,25 +3201,25 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03467132</v>
+        <v>0.03502036</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03438889</v>
+        <v>0.03525088</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7431</v>
+        <v>3.0504</v>
       </c>
       <c r="Z9" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AA9" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AB9" t="n">
-        <v>328.2082</v>
+        <v>330.7939</v>
       </c>
       <c r="AC9" t="n">
-        <v>836.127</v>
+        <v>859.6123</v>
       </c>
       <c r="AD9" t="n">
         <v>8</v>
@@ -3231,7 +3231,7 @@
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.2862</v>
+        <v>5.635</v>
       </c>
     </row>
     <row r="10">
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
         <v>155</v>
@@ -3379,13 +3379,13 @@
         <v>446</v>
       </c>
       <c r="O11" t="n">
-        <v>314.4508</v>
+        <v>437.2914</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="n">
-        <v>28.5864</v>
+        <v>24.294</v>
       </c>
       <c r="R11" t="n">
         <v>109.4975</v>
@@ -3409,7 +3409,7 @@
         <v>0.04030363</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.5663</v>
+        <v>6.3928</v>
       </c>
       <c r="Z11" t="n">
         <v>140</v>
@@ -3471,22 +3471,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N12" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="O12" t="n">
-        <v>340.1493</v>
+        <v>413.0904</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.0149</v>
+        <v>37.5537</v>
       </c>
       <c r="R12" t="n">
         <v>161.8173</v>
@@ -3504,25 +3504,25 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02822801</v>
+        <v>0.02950282</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03281998</v>
+        <v>0.0333433</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8539</v>
+        <v>2.4719</v>
       </c>
       <c r="Z12" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="AA12" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="AB12" t="n">
-        <v>179.6812</v>
+        <v>187.6812</v>
       </c>
       <c r="AC12" t="n">
-        <v>491.0904</v>
+        <v>499.0904</v>
       </c>
       <c r="AD12" t="n">
         <v>4</v>
@@ -3534,7 +3534,7 @@
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.9932</v>
+        <v>8.1251</v>
       </c>
     </row>
     <row r="13">
@@ -3575,10 +3575,10 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N13" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O13" t="n">
         <v>52.3553</v>
@@ -3605,25 +3605,25 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01692219</v>
+        <v>0.01663292</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02022587</v>
+        <v>0.02017454</v>
       </c>
       <c r="Y13" t="n">
         <v>0.6794</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB13" t="n">
-        <v>134.7817</v>
+        <v>131.9533</v>
       </c>
       <c r="AC13" t="n">
-        <v>456.0732</v>
+        <v>455.2447</v>
       </c>
       <c r="AD13" t="n">
         <v>2</v>
@@ -3635,7 +3635,7 @@
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.7831</v>
+        <v>6.1861</v>
       </c>
     </row>
     <row r="14">
@@ -3682,13 +3682,13 @@
         <v>732</v>
       </c>
       <c r="O14" t="n">
-        <v>672.6001</v>
+        <v>858.725</v>
       </c>
       <c r="P14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.0214</v>
+        <v>26.8352</v>
       </c>
       <c r="R14" t="n">
         <v>254.6934</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
         <v>218</v>
@@ -3783,13 +3783,13 @@
         <v>381</v>
       </c>
       <c r="O15" t="n">
-        <v>348.2203</v>
+        <v>359.2914</v>
       </c>
       <c r="P15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.4835</v>
+        <v>19.9606</v>
       </c>
       <c r="R15" t="n">
         <v>202.6934</v>
@@ -3813,7 +3813,7 @@
         <v>0.02327286</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9336</v>
+        <v>5.4269</v>
       </c>
       <c r="Z15" t="n">
         <v>181</v>

--- a/results/682_z29/5_quantification/682_z29_quantification.xlsx
+++ b/results/682_z29/5_quantification/682_z29_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.1538</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9678</v>
+        <v>3.4157</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>264.5385</v>
+        <v>299.6154</v>
       </c>
       <c r="D13" t="n">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="E13" t="n">
-        <v>111.0117</v>
+        <v>121.5172</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>708.9231</v>
+        <v>749.4615</v>
       </c>
       <c r="D14" t="n">
-        <v>732</v>
+        <v>760</v>
       </c>
       <c r="E14" t="n">
-        <v>280.6642</v>
+        <v>292.6931</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1905.5153</v>
+        <v>2269.1392</v>
       </c>
       <c r="D15" t="n">
-        <v>1513.8154</v>
+        <v>1782.6682</v>
       </c>
       <c r="E15" t="n">
-        <v>1766.7778</v>
+        <v>2137.0929</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>82.5385</v>
+        <v>99.5385</v>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>82.2259</v>
+        <v>100.8635</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.8208</v>
+        <v>26.3152</v>
       </c>
       <c r="D17" t="n">
-        <v>24.294</v>
+        <v>24.6963</v>
       </c>
       <c r="E17" t="n">
-        <v>9.0184</v>
+        <v>6.6832</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0349763</v>
+        <v>0.03944967</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03468361</v>
+        <v>0.03863369</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01081229</v>
+        <v>0.01113154</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03703612</v>
+        <v>0.03909379</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03636696</v>
+        <v>0.03760051</v>
       </c>
       <c r="E24" t="n">
-        <v>0.009710369999999999</v>
+        <v>0.009648800000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.3705</v>
+        <v>3.8347</v>
       </c>
       <c r="D25" t="n">
-        <v>3.0504</v>
+        <v>2.9757</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5392</v>
+        <v>1.7283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>200.0769</v>
+        <v>257.3846</v>
       </c>
       <c r="D26" t="n">
-        <v>173</v>
+        <v>258</v>
       </c>
       <c r="E26" t="n">
-        <v>110.6047</v>
+        <v>126.8684</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>464.6154</v>
+        <v>560.7692</v>
       </c>
       <c r="D27" t="n">
-        <v>356</v>
+        <v>471</v>
       </c>
       <c r="E27" t="n">
-        <v>336.1097</v>
+        <v>341.5953</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>295.3183</v>
+        <v>335.9725</v>
       </c>
       <c r="D28" t="n">
-        <v>292.0955</v>
+        <v>343.8061</v>
       </c>
       <c r="E28" t="n">
-        <v>120.9282</v>
+        <v>132.8492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>795.5107</v>
+        <v>842.489</v>
       </c>
       <c r="D29" t="n">
-        <v>815.8549</v>
+        <v>848.1686</v>
       </c>
       <c r="E29" t="n">
-        <v>312.688</v>
+        <v>326.4314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.9231</v>
+        <v>7.1538</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>2.7222</v>
+        <v>2.7642</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.1538</v>
+        <v>9.8462</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>3.7159</v>
+        <v>3.8264</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10.9231</v>
+        <v>11</v>
       </c>
       <c r="D32" t="n">
         <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>3.8829</v>
+        <v>3.9158</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.0539</v>
+        <v>7.0396</v>
       </c>
       <c r="D33" t="n">
-        <v>7.0222</v>
+        <v>7.1612</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6399</v>
+        <v>0.6108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33616</v>
+        <v>36855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03286895</v>
+        <v>0.03603597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>683</v>
+        <v>794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00066782</v>
+        <v>0.00077636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>129.2923</v>
+        <v>149.8171</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03713687</v>
+        <v>0.04073355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03319469</v>
+        <v>0.03647435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03286895</v>
+        <v>0.03603597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03337055</v>
+        <v>0.03653757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.516</v>
+        <v>7.6752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31437</v>
+        <v>34543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>523</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.9678</v>
+        <v>20.3566</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4438</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.4029</v>
+        <v>45.3664</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4474</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5526</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="15">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>1.3257</v>
       </c>
     </row>
   </sheetData>
@@ -2562,22 +2562,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>463</v>
+        <v>525</v>
       </c>
       <c r="N3" t="n">
-        <v>1191</v>
+        <v>1298</v>
       </c>
       <c r="O3" t="n">
-        <v>4157.7964</v>
+        <v>6255.1996</v>
       </c>
       <c r="P3" t="n">
-        <v>190</v>
+        <v>271</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.8831</v>
+        <v>23.0819</v>
       </c>
       <c r="R3" t="n">
         <v>229.5219</v>
@@ -2595,37 +2595,37 @@
         <v>0.999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05059556</v>
+        <v>0.05737078</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04989318</v>
+        <v>0.0543756</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.3569</v>
+        <v>5.6639</v>
       </c>
       <c r="Z3" t="n">
-        <v>377</v>
+        <v>488</v>
       </c>
       <c r="AA3" t="n">
-        <v>1057</v>
+        <v>1248</v>
       </c>
       <c r="AB3" t="n">
-        <v>509.5341</v>
+        <v>577.2619999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>1347.5017</v>
+        <v>1467.6144</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.0028</v>
+        <v>7.3132</v>
       </c>
     </row>
     <row r="4">
@@ -2663,22 +2663,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="N4" t="n">
-        <v>918</v>
+        <v>968</v>
       </c>
       <c r="O4" t="n">
-        <v>5123.5537</v>
+        <v>4890.6004</v>
       </c>
       <c r="P4" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.9895</v>
+        <v>20.5487</v>
       </c>
       <c r="R4" t="n">
         <v>120.8112</v>
@@ -2696,37 +2696,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05656994</v>
+        <v>0.06162374</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05125342</v>
+        <v>0.054045</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.1387</v>
+        <v>6.6219</v>
       </c>
       <c r="Z4" t="n">
-        <v>308</v>
+        <v>357</v>
       </c>
       <c r="AA4" t="n">
-        <v>902</v>
+        <v>968</v>
       </c>
       <c r="AB4" t="n">
-        <v>390.0782</v>
+        <v>428.0488</v>
       </c>
       <c r="AC4" t="n">
-        <v>1018.3402</v>
+        <v>1078.3107</v>
       </c>
       <c r="AD4" t="n">
         <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF4" t="n">
         <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.4637</v>
+        <v>7.7186</v>
       </c>
     </row>
     <row r="5">
@@ -2767,19 +2767,19 @@
         <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="N5" t="n">
-        <v>1192</v>
+        <v>1233</v>
       </c>
       <c r="O5" t="n">
-        <v>4365.2501</v>
+        <v>5608.2127</v>
       </c>
       <c r="P5" t="n">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.1905</v>
+        <v>20.3935</v>
       </c>
       <c r="R5" t="n">
         <v>309.2792</v>
@@ -2797,25 +2797,25 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03468361</v>
+        <v>0.03786074</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04371264</v>
+        <v>0.04521618</v>
       </c>
       <c r="Y5" t="n">
         <v>2.5867</v>
       </c>
       <c r="Z5" t="n">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="AA5" t="n">
-        <v>1007</v>
+        <v>1048</v>
       </c>
       <c r="AB5" t="n">
-        <v>437.6346</v>
+        <v>480.8478</v>
       </c>
       <c r="AC5" t="n">
-        <v>1335.4478</v>
+        <v>1385.4895</v>
       </c>
       <c r="AD5" t="n">
         <v>11</v>
@@ -2827,7 +2827,7 @@
         <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.5622</v>
+        <v>7.4282</v>
       </c>
     </row>
     <row r="6">
@@ -2865,22 +2865,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="N6" t="n">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="O6" t="n">
-        <v>2413.5525</v>
+        <v>3058.8978</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.1355</v>
+        <v>24.8691</v>
       </c>
       <c r="R6" t="n">
         <v>235.2376</v>
@@ -2898,37 +2898,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02855012</v>
+        <v>0.03110685</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03636696</v>
+        <v>0.03760051</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1255</v>
+        <v>2.9757</v>
       </c>
       <c r="Z6" t="n">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AA6" t="n">
-        <v>356</v>
+        <v>504</v>
       </c>
       <c r="AB6" t="n">
-        <v>292.0955</v>
+        <v>319.9949</v>
       </c>
       <c r="AC6" t="n">
-        <v>878.7422</v>
+        <v>910.0559</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.8365</v>
+        <v>7.0246</v>
       </c>
     </row>
     <row r="7">
@@ -2966,22 +2966,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="N7" t="n">
-        <v>858</v>
+        <v>900</v>
       </c>
       <c r="O7" t="n">
-        <v>2568.1038</v>
+        <v>2676.8734</v>
       </c>
       <c r="P7" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.7266</v>
+        <v>22.6854</v>
       </c>
       <c r="R7" t="n">
         <v>214.1665</v>
@@ -2999,28 +2999,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04561769</v>
+        <v>0.05059627</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04347165</v>
+        <v>0.04559964</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.2685</v>
+        <v>4.2023</v>
       </c>
       <c r="Z7" t="n">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="AA7" t="n">
-        <v>662</v>
+        <v>712</v>
       </c>
       <c r="AB7" t="n">
-        <v>437.9777</v>
+        <v>486.5341</v>
       </c>
       <c r="AC7" t="n">
-        <v>959.9675999999999</v>
+        <v>1007.524</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -3029,7 +3029,7 @@
         <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.3633</v>
+        <v>7.115</v>
       </c>
     </row>
     <row r="8">
@@ -3070,19 +3070,19 @@
         <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="N8" t="n">
-        <v>783</v>
+        <v>819</v>
       </c>
       <c r="O8" t="n">
-        <v>1341.7027</v>
+        <v>1415.5017</v>
       </c>
       <c r="P8" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.3946</v>
+        <v>22.4683</v>
       </c>
       <c r="R8" t="n">
         <v>322.8356</v>
@@ -3100,25 +3100,25 @@
         <v>0.7724</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03631791</v>
+        <v>0.03923541</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03661274</v>
+        <v>0.03829608</v>
       </c>
       <c r="Y8" t="n">
         <v>3.7171</v>
       </c>
       <c r="Z8" t="n">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="AA8" t="n">
-        <v>686</v>
+        <v>767</v>
       </c>
       <c r="AB8" t="n">
-        <v>404.4924</v>
+        <v>438.9777</v>
       </c>
       <c r="AC8" t="n">
-        <v>880.997</v>
+        <v>923.3107</v>
       </c>
       <c r="AD8" t="n">
         <v>10</v>
@@ -3127,10 +3127,10 @@
         <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.473</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="9">
@@ -3168,22 +3168,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>301</v>
+        <v>352</v>
       </c>
       <c r="N9" t="n">
-        <v>777</v>
+        <v>809</v>
       </c>
       <c r="O9" t="n">
-        <v>1513.8154</v>
+        <v>1782.6682</v>
       </c>
       <c r="P9" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="n">
-        <v>29.1118</v>
+        <v>30.2147</v>
       </c>
       <c r="R9" t="n">
         <v>229.4802</v>
@@ -3201,28 +3201,28 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03502036</v>
+        <v>0.04095404</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03525088</v>
+        <v>0.03670266</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.0504</v>
+        <v>2.6146</v>
       </c>
       <c r="Z9" t="n">
-        <v>173</v>
+        <v>304</v>
       </c>
       <c r="AA9" t="n">
-        <v>264</v>
+        <v>471</v>
       </c>
       <c r="AB9" t="n">
-        <v>330.7939</v>
+        <v>387.6934</v>
       </c>
       <c r="AC9" t="n">
-        <v>859.6123</v>
+        <v>893.2691</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -3231,7 +3231,7 @@
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.635</v>
+        <v>5.7984</v>
       </c>
     </row>
     <row r="10">
@@ -3269,22 +3269,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N10" t="n">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="O10" t="n">
-        <v>2474.4886</v>
+        <v>2417.4764</v>
       </c>
       <c r="P10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>25.2499</v>
+        <v>24.419</v>
       </c>
       <c r="R10" t="n">
         <v>156.8528</v>
@@ -3302,25 +3302,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02542618</v>
+        <v>0.03004912</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02841114</v>
+        <v>0.03005816</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.4628</v>
+        <v>5.1003</v>
       </c>
       <c r="Z10" t="n">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="AA10" t="n">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="AB10" t="n">
-        <v>208.4802</v>
+        <v>244.7939</v>
       </c>
       <c r="AC10" t="n">
-        <v>643.2691</v>
+        <v>679.5828</v>
       </c>
       <c r="AD10" t="n">
         <v>5</v>
@@ -3332,7 +3332,7 @@
         <v>8</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.9506</v>
+        <v>6.6552</v>
       </c>
     </row>
     <row r="11">
@@ -3370,22 +3370,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="N11" t="n">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="O11" t="n">
-        <v>437.2914</v>
+        <v>444.5341</v>
       </c>
       <c r="P11" t="n">
         <v>18</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.294</v>
+        <v>24.6963</v>
       </c>
       <c r="R11" t="n">
         <v>109.4975</v>
@@ -3403,25 +3403,25 @@
         <v>0.9865</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03651355</v>
+        <v>0.03863369</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04030363</v>
+        <v>0.04111693</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.3928</v>
+        <v>5.4796</v>
       </c>
       <c r="Z11" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="n">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="AB11" t="n">
-        <v>173.0244</v>
+        <v>183.6812</v>
       </c>
       <c r="AC11" t="n">
-        <v>496.333</v>
+        <v>506.9899</v>
       </c>
       <c r="AD11" t="n">
         <v>6</v>
@@ -3433,7 +3433,7 @@
         <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.8163</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="12">
@@ -3474,19 +3474,19 @@
         <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="N12" t="n">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="O12" t="n">
-        <v>413.0904</v>
+        <v>420.0904</v>
       </c>
       <c r="P12" t="n">
         <v>11</v>
       </c>
       <c r="Q12" t="n">
-        <v>37.5537</v>
+        <v>38.19</v>
       </c>
       <c r="R12" t="n">
         <v>161.8173</v>
@@ -3504,28 +3504,28 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02950282</v>
+        <v>0.0315061</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0333433</v>
+        <v>0.03416567</v>
       </c>
       <c r="Y12" t="n">
         <v>2.4719</v>
       </c>
       <c r="Z12" t="n">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="AA12" t="n">
-        <v>318</v>
+        <v>404</v>
       </c>
       <c r="AB12" t="n">
-        <v>187.6812</v>
+        <v>199.0955</v>
       </c>
       <c r="AC12" t="n">
-        <v>499.0904</v>
+        <v>511.5046</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -3534,7 +3534,7 @@
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>8.1251</v>
+        <v>7.8561</v>
       </c>
     </row>
     <row r="13">
@@ -3572,22 +3572,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="N13" t="n">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="O13" t="n">
-        <v>52.3553</v>
+        <v>404.333</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>52.3553</v>
+        <v>25.2708</v>
       </c>
       <c r="R13" t="n">
         <v>147.196</v>
@@ -3605,37 +3605,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01663292</v>
+        <v>0.02285218</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02017454</v>
+        <v>0.02274127</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6794</v>
+        <v>1.3587</v>
       </c>
       <c r="Z13" t="n">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="AA13" t="n">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="AB13" t="n">
-        <v>131.9533</v>
+        <v>179.9239</v>
       </c>
       <c r="AC13" t="n">
-        <v>455.2447</v>
+        <v>510.6295</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.1861</v>
+        <v>6.0685</v>
       </c>
     </row>
     <row r="14">
@@ -3676,19 +3676,19 @@
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="N14" t="n">
-        <v>732</v>
+        <v>760</v>
       </c>
       <c r="O14" t="n">
-        <v>858.725</v>
+        <v>889.6245</v>
       </c>
       <c r="P14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.8352</v>
+        <v>24.7118</v>
       </c>
       <c r="R14" t="n">
         <v>254.6934</v>
@@ -3706,37 +3706,37 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02981086</v>
+        <v>0.03258635</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03093306</v>
+        <v>0.03211629</v>
       </c>
       <c r="Y14" t="n">
         <v>2.7484</v>
       </c>
       <c r="Z14" t="n">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="AA14" t="n">
-        <v>409</v>
+        <v>487</v>
       </c>
       <c r="AB14" t="n">
-        <v>322.1076</v>
+        <v>353.4214</v>
       </c>
       <c r="AC14" t="n">
-        <v>815.8549</v>
+        <v>848.1686</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF14" t="n">
         <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.0222</v>
+        <v>7.1723</v>
       </c>
     </row>
     <row r="15">
@@ -3774,22 +3774,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>218</v>
+        <v>299</v>
       </c>
       <c r="N15" t="n">
-        <v>381</v>
+        <v>473</v>
       </c>
       <c r="O15" t="n">
-        <v>359.2914</v>
+        <v>608.2569</v>
       </c>
       <c r="P15" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="Q15" t="n">
-        <v>19.9606</v>
+        <v>20.9744</v>
       </c>
       <c r="R15" t="n">
         <v>202.6934</v>
@@ -3807,37 +3807,37 @@
         <v>0.8055</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0282713</v>
+        <v>0.03877577</v>
       </c>
       <c r="X15" t="n">
-        <v>0.02327286</v>
+        <v>0.02889255</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.4269</v>
+        <v>5.9203</v>
       </c>
       <c r="Z15" t="n">
-        <v>181</v>
+        <v>290</v>
       </c>
       <c r="AA15" t="n">
-        <v>241</v>
+        <v>403</v>
       </c>
       <c r="AB15" t="n">
-        <v>242.8944</v>
+        <v>343.8061</v>
       </c>
       <c r="AC15" t="n">
-        <v>425.4041</v>
+        <v>538.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
         <v>7</v>
       </c>
       <c r="AG15" t="n">
-        <v>7.0835</v>
+        <v>7.1612</v>
       </c>
     </row>
     <row r="16">
@@ -3857,19 +3857,19 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="N16" t="n">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="O16" t="n">
-        <v>34.3848</v>
+        <v>42.0416</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3848</v>
+        <v>42.0416</v>
       </c>
       <c r="R16" t="n">
         <v>47.4558</v>
@@ -3887,25 +3887,25 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03749701</v>
+        <v>0.03893002</v>
       </c>
       <c r="X16" t="n">
-        <v>0.04508231</v>
+        <v>0.04558886</v>
       </c>
       <c r="Y16" t="n">
         <v>2.1072</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AB16" t="n">
-        <v>174.8823</v>
+        <v>182.5391</v>
       </c>
       <c r="AC16" t="n">
-        <v>606.8305</v>
+        <v>614.4874</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
@@ -3917,7 +3917,7 @@
         <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.6531</v>
+        <v>7.574</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z29/5_quantification/682_z29_quantification.xlsx
+++ b/results/682_z29/5_quantification/682_z29_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>7.8462</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4157</v>
+        <v>3.9549</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>299.6154</v>
+        <v>312.9231</v>
       </c>
       <c r="D13" t="n">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="E13" t="n">
-        <v>121.5172</v>
+        <v>123.6247</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>749.4615</v>
+        <v>777.4615</v>
       </c>
       <c r="D14" t="n">
-        <v>760</v>
+        <v>842</v>
       </c>
       <c r="E14" t="n">
-        <v>292.6931</v>
+        <v>298.445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2269.1392</v>
+        <v>2261.2119</v>
       </c>
       <c r="D15" t="n">
-        <v>1782.6682</v>
+        <v>1997.6926</v>
       </c>
       <c r="E15" t="n">
-        <v>2137.0929</v>
+        <v>1901.2181</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>99.5385</v>
+        <v>99.2308</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E16" t="n">
-        <v>100.8635</v>
+        <v>87.8798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.3152</v>
+        <v>23.6307</v>
       </c>
       <c r="D17" t="n">
-        <v>24.6963</v>
+        <v>22.8286</v>
       </c>
       <c r="E17" t="n">
-        <v>6.6832</v>
+        <v>3.5199</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03944967</v>
+        <v>0.04131445</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03863369</v>
+        <v>0.0409894</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01113154</v>
+        <v>0.01065711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03909379</v>
+        <v>0.04045698</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03760051</v>
+        <v>0.0406043</v>
       </c>
       <c r="E24" t="n">
-        <v>0.009648800000000001</v>
+        <v>0.009464709999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.8347</v>
+        <v>4.2332</v>
       </c>
       <c r="D25" t="n">
-        <v>2.9757</v>
+        <v>4.2023</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7283</v>
+        <v>1.3649</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>257.3846</v>
+        <v>279.9231</v>
       </c>
       <c r="D26" t="n">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="E26" t="n">
-        <v>126.8684</v>
+        <v>125.3379</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>560.7692</v>
+        <v>639.6154</v>
       </c>
       <c r="D27" t="n">
-        <v>471</v>
+        <v>639</v>
       </c>
       <c r="E27" t="n">
-        <v>341.5953</v>
+        <v>314.74</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>335.9725</v>
+        <v>350.5151</v>
       </c>
       <c r="D28" t="n">
-        <v>343.8061</v>
+        <v>338.4092</v>
       </c>
       <c r="E28" t="n">
-        <v>132.8492</v>
+        <v>136.278</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>842.489</v>
+        <v>874.2346</v>
       </c>
       <c r="D29" t="n">
-        <v>848.1686</v>
+        <v>926.0559</v>
       </c>
       <c r="E29" t="n">
-        <v>326.4314</v>
+        <v>334.5057</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.1538</v>
+        <v>7.5385</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>2.7642</v>
+        <v>2.9613</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.8462</v>
+        <v>9.692299999999999</v>
       </c>
       <c r="D31" t="n">
         <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>3.8264</v>
+        <v>3.924</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>11.2308</v>
       </c>
       <c r="D32" t="n">
         <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9158</v>
+        <v>3.8113</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10.2308</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.6757</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.2228</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.2153</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7.0396</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.1612</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.6108</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.1965</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.1922</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5417</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36855</v>
+        <v>37663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03603597</v>
+        <v>0.03682602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00077636</v>
+        <v>0.00080569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149.8171</v>
+        <v>159.589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1611,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04073355</v>
+        <v>0.04158214</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03647435</v>
+        <v>0.03711846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03603597</v>
+        <v>0.03682602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03653757</v>
+        <v>0.03732762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>165</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.6752</v>
+        <v>7.6905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1786,7 +1904,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34543</v>
+        <v>35153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>630</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.3566</v>
+        <v>20.5201</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +2117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.39</v>
+        <v>0.4438</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45.3664</v>
+        <v>44.5674</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2147,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0471</v>
+        <v>50.0433</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.419</v>
+        <v>0.3912</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.581</v>
+        <v>0.6088</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2230,7 +2348,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="26">
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2464,22 +2592,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="N2" t="n">
-        <v>230</v>
+        <v>359</v>
       </c>
       <c r="O2" t="n">
-        <v>90.84059999999999</v>
+        <v>1495.7199</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.3551</v>
+        <v>18.9332</v>
       </c>
       <c r="R2" t="n">
         <v>262.0955</v>
@@ -2497,34 +2625,40 @@
         <v>0.5584</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02282861</v>
+        <v>0.03424291</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01664375</v>
+        <v>0.02597872</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.1446</v>
+        <v>1.5262</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="AA2" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>145.397</v>
+        <v>219.5097</v>
       </c>
       <c r="AC2" t="n">
-        <v>253.6518</v>
+        <v>395.664</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.3418</v>
       </c>
     </row>
     <row r="3">
@@ -2562,22 +2696,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="N3" t="n">
-        <v>1298</v>
+        <v>1315</v>
       </c>
       <c r="O3" t="n">
-        <v>6255.1996</v>
+        <v>6300.6849</v>
       </c>
       <c r="P3" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.0819</v>
+        <v>22.8286</v>
       </c>
       <c r="R3" t="n">
         <v>229.5219</v>
@@ -2595,28 +2729,28 @@
         <v>0.999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05737078</v>
+        <v>0.05857283</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0543756</v>
+        <v>0.05508776</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.6639</v>
+        <v>7.4067</v>
       </c>
       <c r="Z3" t="n">
-        <v>488</v>
+        <v>528</v>
       </c>
       <c r="AA3" t="n">
-        <v>1248</v>
+        <v>1263</v>
       </c>
       <c r="AB3" t="n">
-        <v>577.2619999999999</v>
+        <v>590.333</v>
       </c>
       <c r="AC3" t="n">
-        <v>1467.6144</v>
+        <v>1486.5139</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
@@ -2625,7 +2759,13 @@
         <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.3132</v>
+        <v>7.2892</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>41</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5507</v>
       </c>
     </row>
     <row r="4">
@@ -2663,22 +2803,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="N4" t="n">
-        <v>968</v>
+        <v>940</v>
       </c>
       <c r="O4" t="n">
-        <v>4890.6004</v>
+        <v>4633.4339</v>
       </c>
       <c r="P4" t="n">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.5487</v>
+        <v>21.7532</v>
       </c>
       <c r="R4" t="n">
         <v>120.8112</v>
@@ -2696,37 +2836,43 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06162374</v>
+        <v>0.0588523</v>
       </c>
       <c r="X4" t="n">
-        <v>0.054045</v>
+        <v>0.05248172</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.6219</v>
+        <v>4.9664</v>
       </c>
       <c r="Z4" t="n">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="AA4" t="n">
-        <v>968</v>
+        <v>940</v>
       </c>
       <c r="AB4" t="n">
-        <v>428.0488</v>
+        <v>407.8061</v>
       </c>
       <c r="AC4" t="n">
-        <v>1078.3107</v>
+        <v>1046.0681</v>
       </c>
       <c r="AD4" t="n">
         <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF4" t="n">
         <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.7186</v>
+        <v>7.3901</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.3756</v>
       </c>
     </row>
     <row r="5">
@@ -2764,22 +2910,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>429</v>
+        <v>476</v>
       </c>
       <c r="N5" t="n">
-        <v>1233</v>
+        <v>1282</v>
       </c>
       <c r="O5" t="n">
-        <v>5608.2127</v>
+        <v>4171.4978</v>
       </c>
       <c r="P5" t="n">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.3935</v>
+        <v>19.2235</v>
       </c>
       <c r="R5" t="n">
         <v>309.2792</v>
@@ -2797,37 +2943,43 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03786074</v>
+        <v>0.04200865</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04521618</v>
+        <v>0.04701309</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.5867</v>
+        <v>3.88</v>
       </c>
       <c r="Z5" t="n">
-        <v>386</v>
+        <v>450</v>
       </c>
       <c r="AA5" t="n">
-        <v>1048</v>
+        <v>1148</v>
       </c>
       <c r="AB5" t="n">
-        <v>480.8478</v>
+        <v>539.3036</v>
       </c>
       <c r="AC5" t="n">
-        <v>1385.4895</v>
+        <v>1444.7027</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
         <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.4282</v>
+        <v>7.7077</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>33</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.5484</v>
       </c>
     </row>
     <row r="6">
@@ -2868,19 +3020,19 @@
         <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="N6" t="n">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="O6" t="n">
-        <v>3058.8978</v>
+        <v>2980.1282</v>
       </c>
       <c r="P6" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.8691</v>
+        <v>25.2553</v>
       </c>
       <c r="R6" t="n">
         <v>235.2376</v>
@@ -2898,25 +3050,25 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03110685</v>
+        <v>0.03334399</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03760051</v>
+        <v>0.03846857</v>
       </c>
       <c r="Y6" t="n">
         <v>2.9757</v>
       </c>
       <c r="Z6" t="n">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="AA6" t="n">
-        <v>504</v>
+        <v>702</v>
       </c>
       <c r="AB6" t="n">
-        <v>319.9949</v>
+        <v>338.4092</v>
       </c>
       <c r="AC6" t="n">
-        <v>910.0559</v>
+        <v>926.0559</v>
       </c>
       <c r="AD6" t="n">
         <v>7</v>
@@ -2928,7 +3080,13 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.0246</v>
+        <v>7.1922</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.161</v>
       </c>
     </row>
     <row r="7">
@@ -2969,19 +3127,19 @@
         <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="N7" t="n">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="O7" t="n">
-        <v>2676.8734</v>
+        <v>2686.3587</v>
       </c>
       <c r="P7" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.6854</v>
+        <v>22.5744</v>
       </c>
       <c r="R7" t="n">
         <v>214.1665</v>
@@ -2999,25 +3157,25 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05059627</v>
+        <v>0.05001737</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04559964</v>
+        <v>0.04544764</v>
       </c>
       <c r="Y7" t="n">
         <v>4.2023</v>
       </c>
       <c r="Z7" t="n">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="AA7" t="n">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="AB7" t="n">
-        <v>486.5341</v>
+        <v>481.5341</v>
       </c>
       <c r="AC7" t="n">
-        <v>1007.524</v>
+        <v>1004.524</v>
       </c>
       <c r="AD7" t="n">
         <v>9</v>
@@ -3029,7 +3187,13 @@
         <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.115</v>
+        <v>7.3207</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.4118</v>
       </c>
     </row>
     <row r="8">
@@ -3067,22 +3231,22 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N8" t="n">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="O8" t="n">
-        <v>1415.5017</v>
+        <v>1426.6732</v>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.4683</v>
+        <v>22.2918</v>
       </c>
       <c r="R8" t="n">
         <v>322.8356</v>
@@ -3100,25 +3264,25 @@
         <v>0.7724</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03923541</v>
+        <v>0.03943662</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03829608</v>
+        <v>0.0383896</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7171</v>
+        <v>3.4073</v>
       </c>
       <c r="Z8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AA8" t="n">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AB8" t="n">
-        <v>438.9777</v>
+        <v>440.5635</v>
       </c>
       <c r="AC8" t="n">
-        <v>923.3107</v>
+        <v>924.8964999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>10</v>
@@ -3130,7 +3294,13 @@
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.48</v>
+        <v>7.4798</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2188</v>
       </c>
     </row>
     <row r="9">
@@ -3168,22 +3338,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="N9" t="n">
-        <v>809</v>
+        <v>895</v>
       </c>
       <c r="O9" t="n">
-        <v>1782.6682</v>
+        <v>1997.6926</v>
       </c>
       <c r="P9" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="Q9" t="n">
-        <v>30.2147</v>
+        <v>27.3657</v>
       </c>
       <c r="R9" t="n">
         <v>229.4802</v>
@@ -3201,28 +3371,28 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04095404</v>
+        <v>0.04374636</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03670266</v>
+        <v>0.0406043</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.6146</v>
+        <v>3.4861</v>
       </c>
       <c r="Z9" t="n">
-        <v>304</v>
+        <v>358</v>
       </c>
       <c r="AA9" t="n">
-        <v>471</v>
+        <v>644</v>
       </c>
       <c r="AB9" t="n">
-        <v>387.6934</v>
+        <v>417.664</v>
       </c>
       <c r="AC9" t="n">
-        <v>893.2691</v>
+        <v>999.1097</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -3231,7 +3401,13 @@
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.7984</v>
+        <v>6.2524</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.3151</v>
       </c>
     </row>
     <row r="10">
@@ -3269,22 +3445,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="N10" t="n">
-        <v>584</v>
+        <v>646</v>
       </c>
       <c r="O10" t="n">
-        <v>2417.4764</v>
+        <v>2834.2531</v>
       </c>
       <c r="P10" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.419</v>
+        <v>24.4332</v>
       </c>
       <c r="R10" t="n">
         <v>156.8528</v>
@@ -3302,25 +3478,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03004912</v>
+        <v>0.03091592</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03005816</v>
+        <v>0.03324927</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.1003</v>
+        <v>5.7379</v>
       </c>
       <c r="Z10" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AA10" t="n">
-        <v>407</v>
+        <v>482</v>
       </c>
       <c r="AB10" t="n">
-        <v>244.7939</v>
+        <v>252.0366</v>
       </c>
       <c r="AC10" t="n">
-        <v>679.5828</v>
+        <v>750.3818</v>
       </c>
       <c r="AD10" t="n">
         <v>5</v>
@@ -3329,10 +3505,16 @@
         <v>7</v>
       </c>
       <c r="AF10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.6552</v>
+        <v>6.9231</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.3879</v>
       </c>
     </row>
     <row r="11">
@@ -3370,22 +3552,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="N11" t="n">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="O11" t="n">
-        <v>444.5341</v>
+        <v>509.1615</v>
       </c>
       <c r="P11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.6963</v>
+        <v>23.1437</v>
       </c>
       <c r="R11" t="n">
         <v>109.4975</v>
@@ -3403,37 +3585,43 @@
         <v>0.9865</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03863369</v>
+        <v>0.0409894</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04111693</v>
+        <v>0.04211097</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.4796</v>
+        <v>4.5663</v>
       </c>
       <c r="Z11" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="AA11" t="n">
-        <v>330</v>
+        <v>377</v>
       </c>
       <c r="AB11" t="n">
-        <v>183.6812</v>
+        <v>194.5097</v>
       </c>
       <c r="AC11" t="n">
-        <v>506.9899</v>
+        <v>519.9899</v>
       </c>
       <c r="AD11" t="n">
         <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.63</v>
+        <v>6.8561</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3471,22 +3659,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="N12" t="n">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="O12" t="n">
-        <v>420.0904</v>
+        <v>507.4457</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q12" t="n">
-        <v>38.19</v>
+        <v>31.7154</v>
       </c>
       <c r="R12" t="n">
         <v>161.8173</v>
@@ -3504,25 +3692,25 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0315061</v>
+        <v>0.03460208</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03416567</v>
+        <v>0.03558612</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.4719</v>
+        <v>3.0899</v>
       </c>
       <c r="Z12" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="AA12" t="n">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="AB12" t="n">
-        <v>199.0955</v>
+        <v>220.2376</v>
       </c>
       <c r="AC12" t="n">
-        <v>511.5046</v>
+        <v>534.6468</v>
       </c>
       <c r="AD12" t="n">
         <v>5</v>
@@ -3534,7 +3722,13 @@
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.8561</v>
+        <v>8.570399999999999</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3572,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="N13" t="n">
-        <v>443</v>
+        <v>516</v>
       </c>
       <c r="O13" t="n">
-        <v>404.333</v>
+        <v>645.4701</v>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="Q13" t="n">
-        <v>25.2708</v>
+        <v>18.9844</v>
       </c>
       <c r="R13" t="n">
         <v>147.196</v>
@@ -3605,37 +3799,43 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02285218</v>
+        <v>0.0254556</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02274127</v>
+        <v>0.02648871</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3587</v>
+        <v>2.0381</v>
       </c>
       <c r="Z13" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AA13" t="n">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="AB13" t="n">
-        <v>179.9239</v>
+        <v>199.9949</v>
       </c>
       <c r="AC13" t="n">
-        <v>510.6295</v>
+        <v>597.0854</v>
       </c>
       <c r="AD13" t="n">
         <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.0685</v>
+        <v>6.8366</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.0882</v>
       </c>
     </row>
     <row r="14">
@@ -3673,22 +3873,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>760</v>
+        <v>857</v>
       </c>
       <c r="O14" t="n">
-        <v>889.6245</v>
+        <v>1397.9869</v>
       </c>
       <c r="P14" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.7118</v>
+        <v>26.8844</v>
       </c>
       <c r="R14" t="n">
         <v>254.6934</v>
@@ -3706,37 +3906,43 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03258635</v>
+        <v>0.03957648</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03211629</v>
+        <v>0.03621535</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.7484</v>
+        <v>3.5337</v>
       </c>
       <c r="Z14" t="n">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="AA14" t="n">
-        <v>487</v>
+        <v>639</v>
       </c>
       <c r="AB14" t="n">
-        <v>353.4214</v>
+        <v>432.3625</v>
       </c>
       <c r="AC14" t="n">
-        <v>848.1686</v>
+        <v>959.8377</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.1723</v>
+        <v>6.8891</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0577</v>
       </c>
     </row>
     <row r="15">
@@ -3774,22 +3980,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>299</v>
+        <v>228</v>
       </c>
       <c r="N15" t="n">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="O15" t="n">
-        <v>608.2569</v>
+        <v>368.2914</v>
       </c>
       <c r="P15" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.9744</v>
+        <v>21.6642</v>
       </c>
       <c r="R15" t="n">
         <v>202.6934</v>
@@ -3807,37 +4013,43 @@
         <v>0.8055</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03877577</v>
+        <v>0.02956815</v>
       </c>
       <c r="X15" t="n">
-        <v>0.02889255</v>
+        <v>0.0238837</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.9203</v>
+        <v>4.9336</v>
       </c>
       <c r="Z15" t="n">
-        <v>290</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="n">
-        <v>403</v>
+        <v>249</v>
       </c>
       <c r="AB15" t="n">
-        <v>343.8061</v>
+        <v>254.7229</v>
       </c>
       <c r="AC15" t="n">
-        <v>538.73</v>
+        <v>437.2325</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AF15" t="n">
         <v>7</v>
       </c>
       <c r="AG15" t="n">
-        <v>7.1612</v>
+        <v>7.1254</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3854,22 +4066,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="N16" t="n">
-        <v>540</v>
+        <v>584</v>
       </c>
       <c r="O16" t="n">
-        <v>42.0416</v>
+        <v>363.3503</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.0416</v>
+        <v>21.3735</v>
       </c>
       <c r="R16" t="n">
         <v>47.4558</v>
@@ -3887,28 +4099,28 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03893002</v>
+        <v>0.04943874</v>
       </c>
       <c r="X16" t="n">
-        <v>0.04558886</v>
+        <v>0.0493035</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1072</v>
+        <v>4.2144</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>145</v>
       </c>
       <c r="AA16" t="n">
-        <v>36</v>
+        <v>428</v>
       </c>
       <c r="AB16" t="n">
-        <v>182.5391</v>
+        <v>227.7817</v>
       </c>
       <c r="AC16" t="n">
-        <v>614.4874</v>
+        <v>658.9016</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3917,7 +4129,13 @@
         <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.574</v>
+        <v>7.2011</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
